--- a/data/usa/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/usa/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE15"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,145 +436,95 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>h2h_3_segun_loc</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>h2h_3</t>
+          <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_fouls</t>
+          <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_fouls_against</t>
+          <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
+          <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
+          <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
+          <t>dif_mean_last_match_goals</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goal_attempts</t>
+          <t>mean_last_match_mean_rat_player_start_away_against</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
+          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_points_against</t>
+          <t>dif_mean_pot_player_start</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
+          <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goals</t>
+          <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goals_against</t>
+          <t>dif_mean_age_player_start</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_away_against</t>
+          <t>dif_mean_age_player_miss</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rat_player_start</t>
+          <t>dif_mean_val_player_sub</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_pot_player_start</t>
+          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_pot_player_sub</t>
+          <t>dif_mean_val_player_start</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_rat_player_miss</t>
         </is>
@@ -583,1359 +533,939 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>p0lFJwSk</t>
+          <t>dt32E377</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.483966760054599</v>
+        <v>1.486114019161555</v>
       </c>
       <c r="C2" t="n">
-        <v>1.796276090876211</v>
+        <v>-1.269200575300591</v>
       </c>
       <c r="D2" t="n">
-        <v>1.681677775882537</v>
+        <v>1.814798666684625</v>
       </c>
       <c r="E2" t="n">
-        <v>1.559675568221917</v>
+        <v>-0.9826402503463055</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6396316550302068</v>
+        <v>2.201165663030387</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.7683510198033546</v>
+        <v>0.3844169600682545</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1061354269506152</v>
+        <v>-1.843293104417182</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.750214561086118</v>
+        <v>-1.711098859661412</v>
       </c>
       <c r="J2" t="n">
-        <v>1.417755348268819</v>
+        <v>1.67108166770166</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.392123535954986</v>
+        <v>-1.444220824936966</v>
       </c>
       <c r="L2" t="n">
-        <v>1.401026831356332</v>
+        <v>0.8483057687940567</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3170537807281484</v>
+        <v>0.4267466168936427</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6878073804414545</v>
+        <v>-0.04888644968572821</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.179511007623464</v>
+        <v>-0.9528863866173227</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1057097041209094</v>
+        <v>0.5284692523097181</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.023932191010059</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3043042547073486</v>
+        <v>0.2987803074601311</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7201285983991353</v>
+        <v>1.064671205225445</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1353355754465175</v>
+        <v>0.4663773897508778</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1205253335108742</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.4582206862103052</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.07782592902246702</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-0.7513420192997596</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-0.1801843530584994</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-1.110329421810902</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.1460681215128956</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-0.7277109975625162</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.330363511015098</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.4046355283087306</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.02507691226130642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>MHXbihN8</t>
+          <t>Ik4bFqh1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.680238604486398</v>
+        <v>1.486114019161555</v>
       </c>
       <c r="C3" t="n">
-        <v>1.644741524599442</v>
+        <v>-0.8291015565271521</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.4222282553460458</v>
+        <v>1.663178398229461</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06852474117266777</v>
+        <v>-0.5090480398206494</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5152725433742703</v>
+        <v>0.6214668607298954</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.798981542304008</v>
+        <v>0.8406021275167136</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1061354269506152</v>
+        <v>-1.589830710537498</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03087272944601135</v>
+        <v>-0.09250634443367148</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6490892451641471</v>
+        <v>0.7798280612991041</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.529202516123128</v>
+        <v>-1.909668562984051</v>
       </c>
       <c r="L3" t="n">
-        <v>1.17145870797829</v>
+        <v>1.278451219884303</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2167134479820736</v>
+        <v>0.8757291314503108</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6878073804414545</v>
+        <v>-0.04502436824767021</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6496930715787196</v>
+        <v>-0.6413411543834502</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4816284825947726</v>
+        <v>0.2331137087115843</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.037343185188492</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.07101393426308462</v>
+        <v>0.02088172466180868</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.03843256317725809</v>
+        <v>-0.08900088925918968</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6207316453914619</v>
+        <v>0.03101347612504693</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9472330897979383</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.09272949292346588</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-0.3169492281018934</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.05610186118388617</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-0.7739109581351464</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.268236137539219</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.2207868342578734</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.5756186926329664</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-0.2301988829993881</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.2866765879111786</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0.05223815056334007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>vNmJIcsd</t>
+          <t>0E9gGPxe</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.503593944497779</v>
+        <v>1.486114019161555</v>
       </c>
       <c r="C4" t="n">
-        <v>1.796276090876211</v>
+        <v>1.24565096054763</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.928738307393684</v>
+        <v>1.730565184209534</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.416726637242747</v>
+        <v>1.01143221502488</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5152725433742709</v>
+        <v>2.878179435444883</v>
       </c>
       <c r="G4" t="n">
-        <v>1.629221037803427</v>
+        <v>-0.2169180333865322</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1061354269506152</v>
+        <v>-2.35021789217655</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9442730775048184</v>
+        <v>-1.926911195025111</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4234681080051613</v>
+        <v>3.720964962427538</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.649146623770252</v>
+        <v>-3.428085728057684</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.075029356506836</v>
+        <v>-0.8910595277251975</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7504806766922955</v>
+        <v>0.1644322167201823</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03274012772016646</v>
+        <v>0.1375710398854049</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6673338654468529</v>
+        <v>-0.0449161920536345</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.170260167543083</v>
+        <v>-0.8506706719676163</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1692796133668106</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.276843273090074</v>
+        <v>-0.02826985077498774</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7892852643006886</v>
+        <v>-0.6508016168571793</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2589365137094655</v>
+        <v>-0.2716205372247852</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.013654681858227</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.001356694601756084</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-0.3788308234626806</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.03051932885565126</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-0.9001176460259201</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.4952875019084239</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-0.1752493810691365</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.6451380835957142</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-1.181277462237505</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-0.3823416622691982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>69kBKJCq</t>
+          <t>MNAkH5Nl</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.601729866713678</v>
+        <v>1.486114019161555</v>
       </c>
       <c r="C5" t="n">
-        <v>1.796276090876211</v>
+        <v>-0.6764141418506531</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.928738307393684</v>
+        <v>1.646331701734443</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.416726637242747</v>
+        <v>-2.727453657546093</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.888458924141723</v>
+        <v>-0.1006811631789005</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1174264792766263</v>
+        <v>0.5295667860745825</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1061354269506152</v>
+        <v>0.6913308343796587</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.06669235093851392</v>
+        <v>0.6628368293392736</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7920968922533882</v>
+        <v>-0.5570523483047296</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4325706747779944</v>
+        <v>-2.041534542066103</v>
       </c>
       <c r="L5" t="n">
-        <v>0.343373691507495</v>
+        <v>0.3251834161337294</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.31679480336524</v>
+        <v>0.6027661307408159</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6878073804414545</v>
+        <v>-0.1872369157156706</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4667726636585009</v>
+        <v>-0.01006435066671694</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2158356141300999</v>
+        <v>-0.3352521040509716</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9442627150389926</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.5361523920414405</v>
+        <v>0.004865407474353054</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9641411228516643</v>
+        <v>0.004193914468514088</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.09619826439819477</v>
+        <v>0.5534434310794006</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.04490202784682933</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-0.8708381984691103</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.4124992604179042</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-1.627446576067294</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-0.2664222744245303</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-0.8828144552643686</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-0.5209119135938471</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-1.69943162980959</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-0.02677498439411105</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-0.4038724286410119</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-1.794726053974947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>h29zRLZF</t>
+          <t>lSHwpAFr</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.483966760054599</v>
+        <v>1.662801474102982</v>
       </c>
       <c r="C6" t="n">
-        <v>1.644741524599442</v>
+        <v>1.488154501504422</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2790737550634819</v>
+        <v>1.646331701734443</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5655750168557507</v>
+        <v>-1.231899308517704</v>
       </c>
       <c r="F6" t="n">
-        <v>1.246481538418161</v>
+        <v>0.8471381182013941</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6943134918561</v>
+        <v>0.7161879909398612</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1061354269506152</v>
+        <v>-1.082905922778129</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.248739860191087</v>
+        <v>-1.279474188934014</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.56752928471909</v>
+        <v>-0.2896762663839629</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.117965575618703</v>
+        <v>-0.6118984322160295</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.517767880164489</v>
+        <v>0.8241891200549426</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3170537807281485</v>
+        <v>0.8082492398792773</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03274012772016646</v>
+        <v>-0.2648298397132254</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5941657022787655</v>
+        <v>-0.5449643510832892</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3715025725855821</v>
+        <v>0.1618164737841468</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9232314124968243</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03236950593161363</v>
+        <v>-0.2751126213627895</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.32371115505758</v>
+        <v>0.1891356494573769</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.511631061630343</v>
+        <v>-0.4252573167267228</v>
       </c>
       <c r="U6" t="n">
-        <v>1.146174973928634</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.579614120158562</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-0.7087387840739581</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.005695823233066</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.088645858887095</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-1.110329421810902</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-0.9190485603720054</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-0.411894001314411</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.3643111261830542</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0.003634663979921561</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-0.3755513526936898</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>QF7rPa4S</t>
+          <t>S0BoIo8r</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.483966760054599</v>
+        <v>1.525377898037428</v>
       </c>
       <c r="C7" t="n">
-        <v>1.644741524599442</v>
+        <v>1.048055482730984</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4222282553460458</v>
+        <v>1.663178398229461</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06852474117266777</v>
+        <v>2.207875694247591</v>
       </c>
       <c r="F7" t="n">
-        <v>1.401930427988082</v>
+        <v>-1.183903199042094</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001909686486606733</v>
+        <v>0.2807385129208776</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1061354269506152</v>
+        <v>0.1844060466202906</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3989627284640149</v>
+        <v>0.6628368293392736</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3340883285743854</v>
+        <v>-1.091804512146263</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5353799099041007</v>
+        <v>-1.461193673729704</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.239006587491152</v>
+        <v>-1.330389132092836</v>
       </c>
       <c r="M7" t="n">
-        <v>0.08353061816742612</v>
+        <v>-1.194374036167218</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03274012772016646</v>
+        <v>-0.8303142105941549</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6131089899946759</v>
+        <v>-0.7282330641328389</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2525442507998303</v>
+        <v>0.142682421915599</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.07611660257887688</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-1.437152251121662</v>
+        <v>-1.409455617410666</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7445092957918567</v>
+        <v>-0.5572061008935157</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1868518357974684</v>
+        <v>-1.067236545584822</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.04490202784682933</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.1004823364174291</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-1.318578573658425</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.7152157101601512</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-0.4542620950949788</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.113112296712037</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>-0.2979541545332711</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-0.7405806954368386</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-0.02677498439411105</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-0.8705419771731141</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0.8806559187753661</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nP8vQukM</t>
+          <t>C6QBlj7R</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.483966760054599</v>
+        <v>1.486114019161555</v>
       </c>
       <c r="C8" t="n">
-        <v>1.813113264906963</v>
+        <v>1.164816446895365</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2790737550634819</v>
+        <v>1.663178398229461</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5655750168557507</v>
+        <v>1.01143221502488</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5284557151666243</v>
+        <v>0.3055271002697972</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03290609317835558</v>
+        <v>-0.9011957845592207</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1061354269506152</v>
+        <v>-1.336368316657814</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3302224233476369</v>
+        <v>0.6628368293392736</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9342097047524505</v>
+        <v>0.5124519793783373</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5170211179172961</v>
+        <v>2.200372052365765</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1555855970590657</v>
+        <v>-0.9499025293613276</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9649407239419381</v>
+        <v>-0.2131435971242395</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6878073804414545</v>
+        <v>0.2351841069211847</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3256626346914755</v>
+        <v>-0.203275670041762</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.934276074666247</v>
+        <v>-1.007110988807933</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.72410705971514</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.5834112620953971</v>
+        <v>0.1316604306351903</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7364641739215413</v>
+        <v>-0.2036093470428846</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.587436004168353</v>
+        <v>-0.8677785271673422</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6230623008747609</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.2671684715376392</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-0.7429279386996475</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.179244854967686</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.6856359452490264</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.1146939466324631</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0.9185289886741114</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.218629272941475</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>-0.5876329208029185</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0.8874462283508745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>AszX60rp</t>
+          <t>zkH7PTF8</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.483966760054599</v>
+        <v>1.486114019161555</v>
       </c>
       <c r="C9" t="n">
-        <v>1.661578698630194</v>
+        <v>-1.305127025812708</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.227436296984157</v>
+        <v>1.663178398229461</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.919676361559664</v>
+        <v>-0.8829366270777467</v>
       </c>
       <c r="F9" t="n">
-        <v>2.171772547762925</v>
+        <v>-0.1909496661675002</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.330935801258599</v>
+        <v>-0.009561139091777984</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1061354269506152</v>
+        <v>-0.1535438118859549</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.238505682621801</v>
+        <v>-1.279474188934014</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5597094657333715</v>
+        <v>0.1559505368173151</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.239133602731614</v>
+        <v>-1.988294922348705</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7111511952866038</v>
+        <v>-0.2925711480643939</v>
       </c>
       <c r="M9" t="n">
-        <v>1.75155320788687</v>
+        <v>-0.1469592649887488</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6878073804414545</v>
+        <v>0.7182853048981251</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.365880510420309</v>
+        <v>0.1163043259856013</v>
       </c>
       <c r="P9" t="n">
-        <v>1.582887582686676</v>
+        <v>0.1880007905953171</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.666565664116711</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.4201008751802612</v>
+        <v>-0.3826650774712794</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9191127668802798</v>
+        <v>-0.6583405261075176</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2583564586701814</v>
+        <v>-0.6985607815751573</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4062635031287241</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.04012091207157237</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-0.03665682213128051</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.9884022312182792</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.5105436381545739</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>-0.2025387440117078</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0.3451260836617123</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-0.02677498439411105</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>-1.560977776537957</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>-0.4162932101467402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>jix3jCxF</t>
+          <t>UPVAOmVE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.660611420043218</v>
+        <v>1.505745958599491</v>
       </c>
       <c r="C10" t="n">
-        <v>1.644741524599442</v>
+        <v>-1.13447638588015</v>
       </c>
       <c r="D10" t="n">
-        <v>2.382979786292065</v>
+        <v>1.848492059674662</v>
       </c>
       <c r="E10" t="n">
-        <v>2.056725843905</v>
+        <v>-0.1850112641978317</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6707214329441907</v>
+        <v>-0.01041266019030112</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9202334125929251</v>
+        <v>-0.6731032008349913</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1061354269506152</v>
+        <v>-0.3225187411390775</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7571589433890372</v>
+        <v>-0.4162248474792195</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3809499068718205</v>
+        <v>0.3342012580978261</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9639214356849493</v>
+        <v>-2.805312737739435</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4007657223520058</v>
+        <v>1.356448514584981</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.250887453608129</v>
+        <v>1.466903776176655</v>
       </c>
       <c r="N10" t="n">
-        <v>0.03274012772016646</v>
+        <v>2.257089690130559</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7960293979148941</v>
+        <v>3.165943928998591</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.8031738008457822</v>
+        <v>0.5417583424479904</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1282295646302896</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.5342254520185762</v>
+        <v>0.8980554282686523</v>
       </c>
       <c r="S10" t="n">
-        <v>0.371529818782691</v>
+        <v>1.460895807011638</v>
       </c>
       <c r="T10" t="n">
-        <v>1.313470851476471</v>
+        <v>1.26603866344879</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.39839862077349</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.08442287489421954</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-2.060651813687859</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-0.3559298857002285</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>-1.012833835397349</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0.7511566681152793</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.7680955613235039</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0.9543105705026151</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0.6060993668223089</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>-1.264315323638004</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0.05902846013884847</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>tS5WR1K9</t>
+          <t>8GUEN7pL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.483966760054599</v>
+        <v>1.505745958599491</v>
       </c>
       <c r="C11" t="n">
-        <v>1.829950438937715</v>
+        <v>-0.04770125788859803</v>
       </c>
       <c r="D11" t="n">
-        <v>2.382979786292065</v>
+        <v>1.814798666684625</v>
       </c>
       <c r="E11" t="n">
-        <v>2.056725843905</v>
+        <v>-0.9327884387120261</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.04892587466450898</v>
+        <v>0.7117353637184949</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1608214486450753</v>
+        <v>0.3429455812093038</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1061354269506152</v>
+        <v>-1.589830710537498</v>
       </c>
       <c r="I11" t="n">
-        <v>1.384002319507826</v>
+        <v>-0.9557556858884665</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.24470854914361</v>
+        <v>1.849332388982171</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9639214356849493</v>
+        <v>0.9308900029189849</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6650862790460462</v>
+        <v>-0.7935887698740063</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4168761587484069</v>
+        <v>0.05696429473323499</v>
       </c>
       <c r="N11" t="n">
-        <v>0.03274012772016646</v>
+        <v>0.7328530848700431</v>
       </c>
       <c r="O11" t="n">
-        <v>1.344790621675549</v>
+        <v>-0.5369421881042051</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.0690010674511794</v>
+        <v>-1.171598347985675</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.548948674334682</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.949662396815196</v>
+        <v>-0.04541766653231525</v>
       </c>
       <c r="S11" t="n">
-        <v>2.276294957929073</v>
+        <v>-0.9698649958359657</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3729337500182974</v>
+        <v>-0.5840804591283715</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.04490202784682933</v>
-      </c>
-      <c r="V11" t="n">
-        <v>-0.1398558118954318</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.249757563466352</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-1.033814883964865</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>-0.3878584616324584</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>-0.7311378109000137</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0.1543263473942428</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>-0.5271592005582144</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.9225365424305189</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0.3284123702583202</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>-0.8644536421302952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>KCHNTNkc</t>
+          <t>juKJMRaR</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.503593944497779</v>
+        <v>1.486114019161555</v>
       </c>
       <c r="C12" t="n">
-        <v>1.678415872660947</v>
+        <v>0.9223129059385726</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.824832276165101</v>
+        <v>1.663178398229461</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9255758101934981</v>
+        <v>0.7621731568534814</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3080073572810432</v>
+        <v>-0.8228291870876963</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.14805700177728</v>
+        <v>0.114852997485074</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1061354269506152</v>
+        <v>0.01543111736716786</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.01296291869976031</v>
+        <v>0.8786491647029726</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9776227404759704</v>
+        <v>-1.626556675987797</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1414475546760992</v>
+        <v>-0.08385424755298498</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.9438475717193834</v>
+        <v>0.4560117954270305</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7838411284866843</v>
+        <v>0.2909049296154163</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6223271250011215</v>
+        <v>-0.1809573364327507</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3746612127745034</v>
+        <v>0.2943321668174635</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6196306174971314</v>
+        <v>0.03529902455634595</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.7730455022767985</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.04751769785519794</v>
+        <v>-0.1253025583648178</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7229261461769398</v>
+        <v>0.1047424577309596</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7255462990154675</v>
+        <v>-0.2456291907137835</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.04490202784682933</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.78174182553689</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0.9398798449539625</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-0.4847966626481747</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>-0.9425241058487988</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>-1.420577103465266</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>-2.152541011349165</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>-1.08295159404348</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>-0.02677498439411105</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>-0.01776902439945716</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0.8263334421712988</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>WdOu5vDd</t>
+          <t>Usy7kWiL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.503593944497779</v>
+        <v>1.505745958599491</v>
       </c>
       <c r="C13" t="n">
-        <v>1.661578698630194</v>
+        <v>1.182779672151424</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2790737550634819</v>
+        <v>1.730565184209534</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5655750168557507</v>
+        <v>-1.331602931786263</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.832886940681215</v>
+        <v>-1.003366193064896</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.478168733044406</v>
+        <v>-0.4657463065402371</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1061354269506152</v>
+        <v>1.705180409898395</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8803094676967784</v>
+        <v>-0.8478495182066176</v>
       </c>
       <c r="J13" t="n">
-        <v>0.674626325001512</v>
+        <v>-0.02230018446319613</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.190176824100134</v>
+        <v>2.013235514394517</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5354613049462648</v>
+        <v>-1.28411035976906</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2026750888616723</v>
+        <v>-1.161457088142772</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6223271250011215</v>
+        <v>-1.14738821650217</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6934653522925985</v>
+        <v>-1.809964540462973</v>
       </c>
       <c r="P13" t="n">
-        <v>1.163360306461189</v>
+        <v>-0.9669715780391961</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.5515654135582746</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8785323815223183</v>
+        <v>-0.3914212532835835</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5587222548712183</v>
+        <v>-0.4810326953476346</v>
       </c>
       <c r="T13" t="n">
-        <v>1.294276216752835</v>
+        <v>-0.9849736483941793</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.04490202784682933</v>
-      </c>
-      <c r="V13" t="n">
-        <v>-0.8680693257926948</v>
-      </c>
-      <c r="W13" t="n">
-        <v>-2.147940007393813</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.143957393924675</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.5222619264126657</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0.189756101312145</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.3089711703330622</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.143732023690407</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0.7869206100269995</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.05244547609732189</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>-0.4502447580242822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>h6Py6Kcj</t>
+          <t>dbI3Q902</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.503593944497779</v>
+        <v>1.505745958599491</v>
       </c>
       <c r="C14" t="n">
-        <v>1.813113264906963</v>
+        <v>1.416301600480187</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.824832276165101</v>
+        <v>1.848492059674662</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.9255758101934981</v>
+        <v>0.1140996056078461</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.411639950327657</v>
+        <v>-2.537930743871087</v>
       </c>
       <c r="G14" t="n">
-        <v>0.02903154234188727</v>
+        <v>-0.5901604431170896</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1061354269506152</v>
+        <v>2.719029985417131</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7204004431766794</v>
+        <v>-0.6320371828429185</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.02125910056667061</v>
+        <v>-0.02230018446319613</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.9209145416269993</v>
+        <v>-0.61494484097369</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1116631244739811</v>
+        <v>-0.4216257358675002</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.000684065150212</v>
+        <v>-1.011688498338267</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.27739437772241</v>
+        <v>-0.6753879198421607</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7960293979148942</v>
+        <v>-0.4118855807746827</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5734000742690978</v>
+        <v>1.257753743447996</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.7240345022522559</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.916096344803933</v>
+        <v>0.0225489837993</v>
       </c>
       <c r="S14" t="n">
-        <v>2.046409510101061</v>
+        <v>0.618158021233176</v>
       </c>
       <c r="T14" t="n">
-        <v>1.828882339425962</v>
+        <v>-0.6898964012901841</v>
       </c>
       <c r="U14" t="n">
-        <v>3.113256688982048</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5.467111357845852</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.458153495083015</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-0.9911134667513445</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.1589949904118232</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0.5236417015687457</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.1893266406538567</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0.471208617369014</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>-0.02677498439411105</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.216674522937108</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0.2491571282530839</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>b3GRSs53</t>
+          <t>hQiNHHd2</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.523221128940959</v>
+        <v>1.505745958599491</v>
       </c>
       <c r="C15" t="n">
-        <v>1.661578698630194</v>
+        <v>-1.206329286904385</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.526134286574629</v>
+        <v>1.730565184209534</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.422626085876581</v>
+        <v>2.457134752418988</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4634562468509636</v>
+        <v>-1.544977210996492</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.05233402522395434</v>
+        <v>-1.004874231706598</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1061354269506152</v>
+        <v>2.719029985417131</v>
       </c>
       <c r="I15" t="n">
-        <v>1.294453265776571</v>
+        <v>-0.2004125121155216</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4234681080051613</v>
+        <v>-0.3788016270242184</v>
       </c>
       <c r="K15" t="n">
-        <v>0.492712441356962</v>
+        <v>-1.309090836471686</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.09116597060094145</v>
+        <v>-1.517701287722691</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9172829356642398</v>
+        <v>-1.115374445125994</v>
       </c>
       <c r="N15" t="n">
-        <v>0.03274012772016646</v>
+        <v>-0.01839508347105087</v>
       </c>
       <c r="O15" t="n">
-        <v>1.893551845436204</v>
+        <v>-1.222685897806376</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1145421158974711</v>
+        <v>-0.5427816562738552</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.5683160085033706</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.272374058454519</v>
+        <v>-0.2405592345218507</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6976199623856705</v>
+        <v>0.1260266751371708</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8811157185926014</v>
+        <v>-0.6436818325716853</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9476621402993888</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-0.0811557111554243</v>
-      </c>
-      <c r="W15" t="n">
-        <v>-0.03665682213128051</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.308662860319682</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.83037010455668</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>-0.07617048296302362</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0.82557845384158</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0.3084592243692785</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0.685208660724361</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0.3205947443607139</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>-0.395922281420215</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/usa/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/usa/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,65 +533,65 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>dt32E377</t>
+          <t>trWntSE7</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.486114019161555</v>
+        <v>1.62353759522711</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.269200575300591</v>
+        <v>-1.305127025812708</v>
       </c>
       <c r="D2" t="n">
-        <v>1.814798666684625</v>
+        <v>1.696871791219498</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.9826402503463055</v>
+        <v>-1.231899308517704</v>
       </c>
       <c r="F2" t="n">
-        <v>2.201165663030387</v>
+        <v>-2.537930743871087</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3844169600682545</v>
+        <v>0.1977957552029758</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.843293104417182</v>
+        <v>0.8603057636327814</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.711098859661412</v>
+        <v>0.01539982324817748</v>
       </c>
       <c r="J2" t="n">
-        <v>1.67108166770166</v>
+        <v>-0.02230018446319613</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.444220824936966</v>
+        <v>-1.312282312313046</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8483057687940567</v>
+        <v>1.184503548647141</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4267466168936427</v>
+        <v>0.8707763017608215</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.04888644968572821</v>
+        <v>0.1298106393218398</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9528863866173227</v>
+        <v>-0.3219736874487772</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5284692523097181</v>
+        <v>-0.1241530898047296</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2987803074601311</v>
+        <v>-0.6653697429887105</v>
       </c>
       <c r="S2" t="n">
-        <v>1.064671205225445</v>
+        <v>0.3010221546554695</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4663773897508778</v>
+        <v>0.5906314435806295</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -600,65 +600,65 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ik4bFqh1</t>
+          <t>SvbdWyTh</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.486114019161555</v>
+        <v>1.505745958599491</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.8291015565271521</v>
+        <v>-0.4878002766620366</v>
       </c>
       <c r="D3" t="n">
-        <v>1.663178398229461</v>
+        <v>1.713718487714516</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5090480398206494</v>
+        <v>0.5627659103163628</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6214668607298954</v>
+        <v>-1.99631972593949</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8406021275167136</v>
+        <v>1.89812228841996</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.589830710537498</v>
+        <v>2.719029985417131</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09250634443367148</v>
+        <v>-0.6320371828429185</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7798280612991041</v>
+        <v>-3.230813167512397</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.909668562984051</v>
+        <v>-3.096897575973705</v>
       </c>
       <c r="L3" t="n">
-        <v>1.278451219884303</v>
+        <v>0.4163802377730254</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8757291314503108</v>
+        <v>0.3915758784226204</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.04502436824767021</v>
+        <v>-0.1257118068459143</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6413411543834502</v>
+        <v>-0.0920231253792176</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2331137087115843</v>
+        <v>-0.3841590364167951</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02088172466180868</v>
+        <v>0.1946967541478897</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.08900088925918968</v>
+        <v>1.065323783035108</v>
       </c>
       <c r="T3" t="n">
-        <v>0.03101347612504693</v>
+        <v>0.5519668208610595</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -667,65 +667,65 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0E9gGPxe</t>
+          <t>AoWGqXpJ</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.486114019161555</v>
+        <v>1.662801474102982</v>
       </c>
       <c r="C4" t="n">
-        <v>1.24565096054763</v>
+        <v>1.182779672151424</v>
       </c>
       <c r="D4" t="n">
-        <v>1.730565184209534</v>
+        <v>1.646331701734443</v>
       </c>
       <c r="E4" t="n">
-        <v>1.01143221502488</v>
+        <v>-1.381454743420543</v>
       </c>
       <c r="F4" t="n">
-        <v>2.878179435444883</v>
+        <v>0.9825408726842934</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2169180333865322</v>
+        <v>-1.461059399155056</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.35021789217655</v>
+        <v>2.719029985417131</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.926911195025111</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>3.720964962427538</v>
+        <v>-2.161308839829331</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.428085728057684</v>
+        <v>0.9121763491218614</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.8910595277251975</v>
+        <v>-1.436179924214527</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1644322167201823</v>
+        <v>-1.174104016974865</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1375710398854049</v>
+        <v>-1.89129310652428</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0449161920536345</v>
+        <v>-1.07993235831359</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.8506706719676163</v>
+        <v>-0.5676934966170964</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.02826985077498774</v>
+        <v>-0.6686430976040584</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6508016168571793</v>
+        <v>-0.6042409447361156</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2716205372247852</v>
+        <v>-1.302630393350031</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -734,65 +734,65 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>MNAkH5Nl</t>
+          <t>hIoLKAg0</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1.486114019161555</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.6764141418506531</v>
+        <v>-1.206329286904385</v>
       </c>
       <c r="D5" t="n">
-        <v>1.646331701734443</v>
+        <v>1.781105273694589</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.727453657546093</v>
+        <v>-2.054454200483318</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1006811631789005</v>
+        <v>0.4409298547526964</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5295667860745825</v>
+        <v>0.7161879909398612</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6913308343796587</v>
+        <v>0.4378684404999746</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6628368293392736</v>
+        <v>-0.2004125121155213</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5570523483047296</v>
+        <v>0.5124519793783373</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.041534542066103</v>
+        <v>-0.1421712151998415</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3251834161337294</v>
+        <v>-0.5402194021013857</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6027661307408159</v>
+        <v>-0.191283557099674</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1872369157156706</v>
+        <v>-0.7055340569178128</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.01006435066671694</v>
+        <v>-0.9234730270154574</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3352521040509716</v>
+        <v>-0.4684402113465267</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.004865407474353054</v>
+        <v>-0.5780363655351539</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004193914468514088</v>
+        <v>-0.5372757518483029</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5534434310794006</v>
+        <v>0.5091163106256762</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -801,65 +801,65 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>lSHwpAFr</t>
+          <t>EyfhXHDn</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.662801474102982</v>
+        <v>1.486114019161555</v>
       </c>
       <c r="C6" t="n">
-        <v>1.488154501504422</v>
+        <v>-0.9189176828074458</v>
       </c>
       <c r="D6" t="n">
-        <v>1.646331701734443</v>
+        <v>1.747411880704552</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.231899308517704</v>
+        <v>0.06424779397356667</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8471381182013941</v>
+        <v>-0.6422921811104975</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7161879909398612</v>
+        <v>-0.5486890642581387</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.082905922778129</v>
+        <v>0.522355905126536</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.279474188934014</v>
+        <v>-0.6320371828429185</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2896762663839629</v>
+        <v>-0.3788016270242184</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6118984322160295</v>
+        <v>0.3281362701511459</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8241891200549426</v>
+        <v>-0.162215976214446</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8082492398792773</v>
+        <v>1.680856930403425</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2648298397132254</v>
+        <v>1.188665474198027</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5449643510832892</v>
+        <v>-0.3155304898814469</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1618164737841468</v>
+        <v>-2.311602508757943</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.2751126213627895</v>
+        <v>0.147556516813424</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1891356494573769</v>
+        <v>-0.2755140427931038</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4252573167267228</v>
+        <v>0.4722789287266096</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -868,603 +868,67 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>S0BoIo8r</t>
+          <t>KEflYcbt</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1.525377898037428</v>
       </c>
       <c r="C7" t="n">
-        <v>1.048055482730984</v>
+        <v>-1.269200575300591</v>
       </c>
       <c r="D7" t="n">
-        <v>1.663178398229461</v>
+        <v>1.646331701734443</v>
       </c>
       <c r="E7" t="n">
-        <v>2.207875694247591</v>
+        <v>-1.580861989957662</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.183903199042094</v>
+        <v>-1.544977210996492</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2807385129208776</v>
+        <v>-0.3413321699633847</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1844060466202906</v>
+        <v>1.029280692885904</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6628368293392736</v>
+        <v>-0.6320371828429185</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.091804512146263</v>
+        <v>-1.270055233426774</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.461193673729704</v>
+        <v>0.05395948196071264</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.330389132092836</v>
+        <v>0.1142753700046404</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.194374036167218</v>
+        <v>0.1137903330377356</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8303142105941549</v>
+        <v>0.5582412318338529</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7282330641328389</v>
+        <v>-0.8337902793942819</v>
       </c>
       <c r="P7" t="n">
-        <v>0.142682421915599</v>
+        <v>0.4786800122701402</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-1.409455617410666</v>
+        <v>0.1394158865595751</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5572061008935157</v>
+        <v>1.16364468595276</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.067236545584822</v>
+        <v>-0.2115410271891691</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>C6QBlj7R</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.486114019161555</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1.164816446895365</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.663178398229461</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1.01143221502488</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.3055271002697972</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-0.9011957845592207</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-1.336368316657814</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.6628368293392736</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.5124519793783373</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2.200372052365765</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-0.9499025293613276</v>
-      </c>
-      <c r="M8" t="n">
-        <v>-0.2131435971242395</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.2351841069211847</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-0.203275670041762</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-1.007110988807933</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.1316604306351903</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-0.2036093470428846</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.8677785271673422</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>zkH7PTF8</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1.486114019161555</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-1.305127025812708</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.663178398229461</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-0.8829366270777467</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-0.1909496661675002</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-0.009561139091777984</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.1535438118859549</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-1.279474188934014</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.1559505368173151</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-1.988294922348705</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-0.2925711480643939</v>
-      </c>
-      <c r="M9" t="n">
-        <v>-0.1469592649887488</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.7182853048981251</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.1163043259856013</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.1880007905953171</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>-0.3826650774712794</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-0.6583405261075176</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.6985607815751573</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>UPVAOmVE</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1.505745958599491</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-1.13447638588015</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.848492059674662</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-0.1850112641978317</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-0.01041266019030112</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-0.6731032008349913</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.3225187411390775</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-0.4162248474792195</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.3342012580978261</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-2.805312737739435</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.356448514584981</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.466903776176655</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.257089690130559</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.165943928998591</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.5417583424479904</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.8980554282686523</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.460895807011638</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.26603866344879</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>8GUEN7pL</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.505745958599491</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.04770125788859803</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.814798666684625</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-0.9327884387120261</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.7117353637184949</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.3429455812093038</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-1.589830710537498</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-0.9557556858884665</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.849332388982171</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.9308900029189849</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-0.7935887698740063</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.05696429473323499</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.7328530848700431</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-0.5369421881042051</v>
-      </c>
-      <c r="P11" t="n">
-        <v>-1.171598347985675</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>-0.04541766653231525</v>
-      </c>
-      <c r="S11" t="n">
-        <v>-0.9698649958359657</v>
-      </c>
-      <c r="T11" t="n">
-        <v>-0.5840804591283715</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>juKJMRaR</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.486114019161555</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.9223129059385726</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.663178398229461</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.7621731568534814</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-0.8228291870876963</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.114852997485074</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.01543111736716786</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.8786491647029726</v>
-      </c>
-      <c r="J12" t="n">
-        <v>-1.626556675987797</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-0.08385424755298498</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.4560117954270305</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.2909049296154163</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-0.1809573364327507</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.2943321668174635</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.03529902455634595</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>-0.1253025583648178</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.1047424577309596</v>
-      </c>
-      <c r="T12" t="n">
-        <v>-0.2456291907137835</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Usy7kWiL</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.505745958599491</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1.182779672151424</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.730565184209534</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-1.331602931786263</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-1.003366193064896</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-0.4657463065402371</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.705180409898395</v>
-      </c>
-      <c r="I13" t="n">
-        <v>-0.8478495182066176</v>
-      </c>
-      <c r="J13" t="n">
-        <v>-0.02230018446319613</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2.013235514394517</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-1.28411035976906</v>
-      </c>
-      <c r="M13" t="n">
-        <v>-1.161457088142772</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-1.14738821650217</v>
-      </c>
-      <c r="O13" t="n">
-        <v>-1.809964540462973</v>
-      </c>
-      <c r="P13" t="n">
-        <v>-0.9669715780391961</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>-0.3914212532835835</v>
-      </c>
-      <c r="S13" t="n">
-        <v>-0.4810326953476346</v>
-      </c>
-      <c r="T13" t="n">
-        <v>-0.9849736483941793</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>dbI3Q902</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.505745958599491</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1.416301600480187</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.848492059674662</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.1140996056078461</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-2.537930743871087</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-0.5901604431170896</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2.719029985417131</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-0.6320371828429185</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-0.02230018446319613</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-0.61494484097369</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-0.4216257358675002</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-1.011688498338267</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-0.6753879198421607</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-0.4118855807746827</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.257753743447996</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.0225489837993</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.618158021233176</v>
-      </c>
-      <c r="T14" t="n">
-        <v>-0.6898964012901841</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>hQiNHHd2</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.505745958599491</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-1.206329286904385</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1.730565184209534</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2.457134752418988</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-1.544977210996492</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-1.004874231706598</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2.719029985417131</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-0.2004125121155216</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-0.3788016270242184</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-1.309090836471686</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-1.517701287722691</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-1.115374445125994</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-0.01839508347105087</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-1.222685897806376</v>
-      </c>
-      <c r="P15" t="n">
-        <v>-0.5427816562738552</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>-0.2405592345218507</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.1260266751371708</v>
-      </c>
-      <c r="T15" t="n">
-        <v>-0.6436818325716853</v>
-      </c>
-      <c r="U15" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/usa/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/usa/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,80 +451,85 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_away_against</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_start</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_sub</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_start</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_rat_player_miss</t>
         </is>
@@ -533,403 +538,1331 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>trWntSE7</t>
+          <t>foKU4Bi8</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.62353759522711</v>
+        <v>1.505745958599491</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.305127025812708</v>
+        <v>1.24565096054763</v>
       </c>
       <c r="D2" t="n">
         <v>1.696871791219498</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.231899308517704</v>
+        <v>-0.7832330038091871</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.537930743871087</v>
+        <v>-1.60149674290068</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1977957552029758</v>
+        <v>-1.183903199042094</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8603057636327814</v>
+        <v>0.40515264949773</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01539982324817748</v>
+        <v>0.522355905126536</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.02230018446319613</v>
+        <v>-2.142723530388809</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.312282312313046</v>
+        <v>1.047204143219871</v>
       </c>
       <c r="L2" t="n">
-        <v>1.184503548647141</v>
+        <v>-2.705216449987372</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8707763017608215</v>
+        <v>-0.04384810582203924</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1298106393218398</v>
+        <v>0.07775041357904083</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3219736874487772</v>
+        <v>0.05688736177061154</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1241530898047296</v>
+        <v>-0.0449161920536345</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.4099556878288266</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.6653697429887105</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3010221546554695</v>
+        <v>-0.1139149636433607</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5906314435806295</v>
+        <v>-0.2166278007811902</v>
       </c>
       <c r="U2" t="n">
+        <v>-0.1747735727582516</v>
+      </c>
+      <c r="V2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SvbdWyTh</t>
+          <t>l8RwqFCb</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.505745958599491</v>
+        <v>1.662801474102982</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.4878002766620366</v>
+        <v>1.182779672151424</v>
       </c>
       <c r="D3" t="n">
-        <v>1.713718487714516</v>
+        <v>1.646331701734443</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5627659103163628</v>
+        <v>-1.929824671397619</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.99631972593949</v>
+        <v>-1.057115394908967</v>
       </c>
       <c r="G3" t="n">
-        <v>1.89812228841996</v>
+        <v>2.336568417513286</v>
       </c>
       <c r="H3" t="n">
-        <v>2.719029985417131</v>
+        <v>-0.4657463065402371</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6320371828429185</v>
+        <v>0.3533809758734133</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.230813167512397</v>
+        <v>0.01539982324817748</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.096897575973705</v>
+        <v>0.1559505368173149</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4163802377730254</v>
+        <v>0.589547154976089</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3915758784226204</v>
+        <v>-0.7348245445529042</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1257118068459143</v>
+        <v>-0.2504849389266325</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0920231253792176</v>
+        <v>-1.268206636734574</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3841590364167951</v>
+        <v>-1.638533723706311</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9687384944871906</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1946967541478897</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.065323783035108</v>
+        <v>-0.1419242741019831</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5519668208610595</v>
+        <v>-0.8464277899262392</v>
       </c>
       <c r="U3" t="n">
+        <v>-0.1532215560423525</v>
+      </c>
+      <c r="V3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AoWGqXpJ</t>
+          <t>AHSZqech</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.662801474102982</v>
+        <v>1.486114019161555</v>
       </c>
       <c r="C4" t="n">
-        <v>1.182779672151424</v>
+        <v>0.2127655083242534</v>
       </c>
       <c r="D4" t="n">
-        <v>1.646331701734443</v>
+        <v>1.781105273694589</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.381454743420543</v>
+        <v>-0.9327884387120261</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9825408726842934</v>
+        <v>0.3285825817972088</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.461059399155056</v>
+        <v>-1.725514216973691</v>
       </c>
       <c r="H4" t="n">
-        <v>2.719029985417131</v>
+        <v>1.276051605535697</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-2.35021789217655</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.161308839829331</v>
+        <v>1.31027383543037</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9121763491218614</v>
+        <v>0.5124519793783373</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.436179924214527</v>
+        <v>1.965363376773978</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.174104016974865</v>
+        <v>-1.655877865473172</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.89129310652428</v>
+        <v>-0.7689490489361736</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.07993235831359</v>
+        <v>-0.4589752785547459</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5676934966170964</v>
+        <v>-0.0449161920536345</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.057432111789437</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.6686430976040584</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6042409447361156</v>
+        <v>-0.7002548792827562</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.302630393350031</v>
+        <v>-2.694175216714962</v>
       </c>
       <c r="U4" t="n">
+        <v>-0.5608119931229483</v>
+      </c>
+      <c r="V4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hIoLKAg0</t>
+          <t>xUcLQXdU</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.486114019161555</v>
+        <v>1.505745958599491</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.206329286904385</v>
+        <v>1.416301600480187</v>
       </c>
       <c r="D5" t="n">
-        <v>1.781105273694589</v>
+        <v>1.680025094724479</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.054454200483318</v>
+        <v>1.759209389539074</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4409298547526964</v>
+        <v>1.516323704688217</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7161879909398612</v>
+        <v>-0.1006811631789005</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4378684404999746</v>
+        <v>2.520192971304222</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2004125121155213</v>
+        <v>1.705180409898395</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5124519793783373</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1421712151998415</v>
+        <v>-0.5570523483047296</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5402194021013857</v>
+        <v>0.719817396137467</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.191283557099674</v>
+        <v>0.9539472286388812</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7055340569178128</v>
+        <v>-0.6834382218982967</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9234730270154574</v>
+        <v>-0.7149667063527663</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4684402113465267</v>
+        <v>0.4061076376593878</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.680614488881718</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.5780363655351539</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5372757518483029</v>
+        <v>-0.120837141515316</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5091163106256762</v>
+        <v>0.286149817818491</v>
       </c>
       <c r="U5" t="n">
+        <v>0.1277111196666239</v>
+      </c>
+      <c r="V5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>EyfhXHDn</t>
+          <t>EkZQoHSu</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.486114019161555</v>
+        <v>1.682433413540919</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.9189176828074458</v>
+        <v>-0.03871964526056867</v>
       </c>
       <c r="D6" t="n">
-        <v>1.747411880704552</v>
+        <v>1.646331701734443</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06424779397356667</v>
+        <v>-1.082343873614865</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6422921811104975</v>
+        <v>0.03164730107445676</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5486890642581387</v>
+        <v>-0.371486672144699</v>
       </c>
       <c r="H6" t="n">
-        <v>0.522355905126536</v>
+        <v>0.7783950592282873</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6320371828429185</v>
+        <v>0.6913308343796587</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3788016270242184</v>
+        <v>0.6628368293392736</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3281362701511459</v>
+        <v>-2.161308839829331</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.162215976214446</v>
+        <v>0.6153690958744571</v>
       </c>
       <c r="M6" t="n">
-        <v>1.680856930403425</v>
+        <v>0.720514281717389</v>
       </c>
       <c r="N6" t="n">
-        <v>1.188665474198027</v>
+        <v>-0.1967853069301546</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3155304898814469</v>
+        <v>-0.5069857905825147</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.311602508757943</v>
+        <v>0.9112543269379719</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>0.9281072915942485</v>
       </c>
       <c r="R6" t="n">
-        <v>0.147556516813424</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2755140427931038</v>
+        <v>-0.2724646145738592</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4722789287266096</v>
+        <v>-0.2730575346845301</v>
       </c>
       <c r="U6" t="n">
+        <v>0.115577714834023</v>
+      </c>
+      <c r="V6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
+          <t>htYUpyrn</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.505745958599491</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.425283213108217</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.696871791219498</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-3.325675397157449</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.704064827579225</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-1.183903199042094</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.271364698150517</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.6913308343796587</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.01539982324817748</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.5570523483047296</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.1888828161507944</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.4810652780168685</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.1946407470405924</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.1896759637498451</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.9055747676008451</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.01591852713794537</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.2523641513343919</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.6378575972984013</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.3986970721605224</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>dKkDSgSH</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.505745958599491</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.2003886725650971</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.680025094724479</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.8618767801220406</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3.594870669747482</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-2.267125234905288</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.5486890642581389</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.6913308343796587</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.01539982324817748</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.2005509057437071</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-2.084619465924596</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.132858400438903</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.8946633614712054</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.757425907566879</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.696035790638628</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.7788760079382698</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.8803364960602643</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.9604560837780212</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.7979003745912392</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>A3m1Vera</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.486114019161555</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-1.179384449020297</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.831645363179644</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.3345666991006706</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-1.749964383262056</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.607373926479085</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.40515264949773</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-1.843293104417182</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.6628368293392736</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.581956307061404</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.565848628267925</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.4959846044519273</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.04145036600554177</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.739677370410409</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.3455987451956497</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.1544842240974258</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.5006047552454505</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.6443678966268347</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-1.107904949215873</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8lOY3V6E</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.486114019161555</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.397984150381743</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.646331701734443</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.460098519733396</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.961726625772345</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-2.537930743871087</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-1.585473535731909</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.719029985417131</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.6628368293392736</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-2.161308839829331</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-1.285589968912503</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.8487815870117064</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.1700084523884368</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.4934744920220367</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.3249233483110439</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-1.1466464352598</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0.2925316937936701</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.1997216390533094</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.5363559905488536</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ITj9TZCB</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.505745958599491</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.218706122663541</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.663178398229461</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.559802143001956</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-2.046899663984808</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.6214668607298952</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.524879878689402</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.04313026840464</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.8689534219393596</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.004346539335786886</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.3572948536840305</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-1.133592168243821</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.6614544481034287</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.3434654390881352</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.809228912406108</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.3243115565055278</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.3594874943053419</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.2165299199474796</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>lfn5UFc5</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.505745958599491</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.9223129059385726</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.663178398229461</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.4132104754135239</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.813258985410969</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.253346381650092</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.151637468958845</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.6913308343796587</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-1.279474188934014</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.5124519793783373</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.4260565516477354</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.2786234786363694</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.1761936587845546</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-1.370258583002284</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.0449161920536345</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.5938300534444186</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.09347075029184576</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.9850303157760573</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.573965285557133</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>vquIRDsO</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.682433413540919</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.164816446895365</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.646331701734443</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.609653954636235</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.763769771957177</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8020038667070943</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-1.585473535731909</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.8294435288984455</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.6628368293392736</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.5570523483047296</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.9290150771812437</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.8656454365765585</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.5823700872144754</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.05194646981657778</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.1661914884875794</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.1913241854915561</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.600433213550304</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.4335319194785925</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.3309400124134132</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>jDDw3kMK</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.505745958599491</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.6764141418506531</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.663178398229461</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.160987649927718</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-1.749964383262056</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-2.267125234905288</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.2169180333865322</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.212105197657763</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.01539982324817748</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-1.091804512146263</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.9213265217452242</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.0260236731337764</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.2126014255865129</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.2691974268746732</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.2277026561284581</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.2683019140112201</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.5273482844407906</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.8716722260055587</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.2031602493867335</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>trWntSE7</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.505745958599491</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-1.305127025812708</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.696871791219498</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-1.231899308517704</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-1.255072248724135</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-2.537930743871087</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1977957552029758</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8603057636327814</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-1.279474188934014</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.02230018446319613</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-1.270502992207852</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.209748613354146</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.016243205691512</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.1417832973186906</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.3219736874487772</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.2947494481333916</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.061404349769643</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.6645508261711883</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.3144783620208266</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.6660188663420447</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.4245322947440672</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AoWGqXpJ</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.505745958599491</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.182779672151424</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.646331701734443</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-1.381454743420543</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.8591585410937995</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9825408726842934</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-1.461059399155056</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.719029985417131</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-2.161308839829331</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.9121763491218614</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-1.502244679959345</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-1.132698390401482</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-1.857832296685331</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-1.01311401317092</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.625332776615377</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.6477407742304916</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.8070128741975213</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.7049692883607892</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-1.31417565046972</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.8796239356685686</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>SvbdWyTh</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.682433413540919</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.4878002766620366</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.713718487714516</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.5627659103163628</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-1.749964383262056</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-1.99631972593949</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.89812228841996</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.719029985417131</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.01539982324817748</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-3.230813167512397</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-3.066433488396978</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.3484385717521059</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.4508570618426563</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.3395886254272084</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0.09252426296778681</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0.5309113914638595</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.268236137539219</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.1118241078406951</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.7854978474796603</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.5457741986610256</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-0.7573605097485532</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>hIoLKAg0</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.486114019161555</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-1.206329286904385</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.781105273694589</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-2.054454200483318</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-1.675730563081368</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.4409298547526964</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.7161879909398612</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.4378684404999746</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.6320371828429185</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.5124519793783373</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.09749055342066222</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.5558557338551776</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.2270825517488297</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.5376586831843403</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.907230799814482</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.4773065511213163</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.3654042086373105</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.4152971284087136</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.4077168485667712</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.4381040992471517</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
           <t>KEflYcbt</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B19" t="n">
         <v>1.525377898037428</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C19" t="n">
         <v>-1.269200575300591</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D19" t="n">
         <v>1.646331701734443</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E19" t="n">
         <v>-1.580861989957662</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F19" t="n">
+        <v>-0.1168203392869193</v>
+      </c>
+      <c r="G19" t="n">
         <v>-1.544977210996492</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H19" t="n">
         <v>-0.3413321699633847</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I19" t="n">
         <v>1.029280692885904</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J19" t="n">
         <v>-0.6320371828429185</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K19" t="n">
         <v>-1.270055233426774</v>
       </c>
-      <c r="K7" t="n">
-        <v>0.05395948196071264</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.1142753700046404</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.1137903330377356</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.5582412318338529</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-0.8337902793942819</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.4786800122701402</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.1394158865595751</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.16364468595276</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-0.2115410271891691</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
+      <c r="L19" t="n">
+        <v>-0.1392698735258687</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-0.007179991156510987</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-0.0517622518599371</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.738992713748828</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-0.6756813702004395</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.5666359625008918</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.23407719869134</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.271512508361441</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.059388828608515</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.21164269749548</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.3566081692329476</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>EyfhXHDn</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.603905655789173</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.9189176828074458</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.747411880704552</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.06424779397356667</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.922453143242713</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.6422921811104975</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.5486890642581387</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.522355905126536</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-1.495286524297713</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.3788016270242184</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.3712211940096389</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-0.2116300340794384</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.62976306471112</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.145919073730525</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-0.3026440947467898</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-2.28489772099319</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-1.558464961978317</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.1631020661870673</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.3183478908927143</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.4452169146510656</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-1.001887361588584</v>
       </c>
     </row>
   </sheetData>

--- a/data/usa/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/usa/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:AI28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,1433 +436,3111 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>id_team_away</t>
+          <t>id_team_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_match_mean_rat_player_start_home_against</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_away_against</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>foKU4Bi8</t>
+          <t>YJuQfCBA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.505745958599491</v>
+        <v>1.568324270223589</v>
       </c>
       <c r="C2" t="n">
-        <v>1.24565096054763</v>
+        <v>-1.282671671996979</v>
       </c>
       <c r="D2" t="n">
-        <v>1.696871791219498</v>
+        <v>1.60132550109786</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7832330038091871</v>
+        <v>1.659017958058589</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.60149674290068</v>
+        <v>-0.679560351381822</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.183903199042094</v>
+        <v>-0.1731686280403403</v>
       </c>
       <c r="H2" t="n">
-        <v>0.40515264949773</v>
+        <v>0.9356568979926685</v>
       </c>
       <c r="I2" t="n">
-        <v>0.522355905126536</v>
+        <v>-0.8669218191866657</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.142723530388809</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1.047204143219871</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-2.705216449987372</v>
+        <v>0.6808955547318705</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.04384810582203924</v>
+        <v>-0.3316021885201621</v>
       </c>
       <c r="N2" t="n">
-        <v>0.07775041357904083</v>
+        <v>0.951585314197482</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05688736177061154</v>
+        <v>-1.861822897909815</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.0449161920536345</v>
+        <v>0.3465795990479323</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.4099556878288266</v>
+        <v>-1.063836661606353</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-0.09260750032261125</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1139149636433607</v>
+        <v>0.6648411163614255</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2166278007811902</v>
+        <v>-0.6872102113855134</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1747735727582516</v>
+        <v>-0.6848282587091638</v>
       </c>
       <c r="V2" t="n">
+        <v>0.03939785194020153</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.8522667083608023</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.314947103600061</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-0.6955397613782694</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.125333233813317</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.2439762976822378</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.2875069191276374</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.9554504184993696</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.149886600955216</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.02360725700915565</v>
+      </c>
+      <c r="AI2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>l8RwqFCb</t>
+          <t>GroLehd4</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.662801474102982</v>
+        <v>1.588039410835988</v>
       </c>
       <c r="C3" t="n">
-        <v>1.182779672151424</v>
+        <v>0.2804556200013386</v>
       </c>
       <c r="D3" t="n">
-        <v>1.646331701734443</v>
+        <v>1.60132550109786</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.929824671397619</v>
+        <v>1.607989243553732</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.057115394908967</v>
+        <v>-0.679560351381822</v>
       </c>
       <c r="G3" t="n">
-        <v>2.336568417513286</v>
+        <v>-0.1731686280403403</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4657463065402371</v>
+        <v>1.06639364431877</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3533809758734133</v>
+        <v>0.2281096086090155</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01539982324817748</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1559505368173149</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.589547154976089</v>
+        <v>-1.008090538971289</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7348245445529042</v>
+        <v>-0.01778807715817907</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2504849389266325</v>
+        <v>-0.01274901706359035</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.268206636734574</v>
+        <v>2.24652137003832</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.638533723706311</v>
+        <v>0.2447638443965733</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9687384944871906</v>
+        <v>0.5040849095757589</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>0.5011472361027797</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1419242741019831</v>
+        <v>-0.3470752261638085</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8464277899262392</v>
+        <v>0.9524733039131357</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1532215560423525</v>
+        <v>0.2451793384682218</v>
       </c>
       <c r="V3" t="n">
+        <v>-0.0009229686173303468</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.3625487572669392</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.04981521047964251</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.3776888968339119</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.1419727559823643</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-0.8229235632619083</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.7237279846541991</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-0.7788427969060643</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-0.2582071306215351</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.539252282105907</v>
+      </c>
+      <c r="AI3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AHSZqech</t>
+          <t>xhnHdYtb</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.486114019161555</v>
+        <v>1.568324270223589</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2127655083242534</v>
+        <v>1.135115146561569</v>
       </c>
       <c r="D4" t="n">
-        <v>1.781105273694589</v>
+        <v>1.633539779427207</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9327884387120261</v>
+        <v>1.624998815055351</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3285825817972088</v>
+        <v>-0.679560351381822</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.725514216973691</v>
+        <v>-0.1731686280403403</v>
       </c>
       <c r="H4" t="n">
-        <v>1.276051605535697</v>
+        <v>-0.09012372702751278</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.35021789217655</v>
+        <v>-2.030392711219577</v>
       </c>
       <c r="J4" t="n">
-        <v>1.31027383543037</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5124519793783373</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.965363376773978</v>
+        <v>0.1404200047468596</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.655877865473172</v>
+        <v>0.8608914346553737</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7689490489361736</v>
+        <v>0.07997543786535893</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4589752785547459</v>
+        <v>1.032692381780917</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.0449161920536345</v>
+        <v>-0.4679464381629391</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.057432111789437</v>
+        <v>1.19511417347061</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.04441282346786362</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7002548792827562</v>
+        <v>0.6790138313127252</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.694175216714962</v>
+        <v>-0.4927936222385033</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5608119931229483</v>
+        <v>-1.470092897603552</v>
       </c>
       <c r="V4" t="n">
+        <v>-0.1687375621566312</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.9406616055409742</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.048388351855706</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0.1320911867840418</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.3307099722899967</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.128384218336234</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.009218722680771972</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-0.829954394089393</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.6183889877220753</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2.011246626280633</v>
+      </c>
+      <c r="AI4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xUcLQXdU</t>
+          <t>rVnDcERi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.505745958599491</v>
+        <v>1.568324270223589</v>
       </c>
       <c r="C5" t="n">
-        <v>1.416301600480187</v>
+        <v>0.03305417810232432</v>
       </c>
       <c r="D5" t="n">
-        <v>1.680025094724479</v>
+        <v>1.617432640262533</v>
       </c>
       <c r="E5" t="n">
-        <v>1.759209389539074</v>
+        <v>1.624998815055351</v>
       </c>
       <c r="F5" t="n">
-        <v>1.516323704688217</v>
+        <v>-0.679560351381822</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1006811631789005</v>
+        <v>-0.1731686280403403</v>
       </c>
       <c r="H5" t="n">
-        <v>2.520192971304222</v>
+        <v>1.06639364431877</v>
       </c>
       <c r="I5" t="n">
-        <v>1.705180409898395</v>
+        <v>-0.7756692002036921</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5570523483047296</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.719817396137467</v>
+        <v>-0.7547426249158149</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9539472286388812</v>
+        <v>0.9236542569277709</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6834382218982967</v>
+        <v>2.08900529465926</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7149667063527663</v>
+        <v>-1.612832336215989</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4061076376593878</v>
+        <v>0.4483953536992911</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.680614488881718</v>
+        <v>-0.2107729496258117</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-0.8690560018019682</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.120837141515316</v>
+        <v>-1.355546014000712</v>
       </c>
       <c r="T5" t="n">
-        <v>0.286149817818491</v>
+        <v>-3.51830759675483</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1277111196666239</v>
+        <v>0.7468039606921811</v>
       </c>
       <c r="V5" t="n">
+        <v>-0.8799976564982432</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.3891342486682206</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-0.1509391972050448</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-0.2277706666447524</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0.7459428200862437</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.041448237863352</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.587044377343323</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.1293391359671632</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-0.9007939735328983</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.06555212691794998</v>
+      </c>
+      <c r="AI5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>EkZQoHSu</t>
+          <t>URr9bfCo</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.682433413540919</v>
+        <v>1.745760535735183</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.03871964526056867</v>
+        <v>-1.260180631824341</v>
       </c>
       <c r="D6" t="n">
-        <v>1.646331701734443</v>
+        <v>1.617432640262533</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.082343873614865</v>
+        <v>1.676027529560207</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03164730107445676</v>
+        <v>-0.679560351381822</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.371486672144699</v>
+        <v>-0.1731686280403403</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7783950592282873</v>
+        <v>1.368093828148235</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6913308343796587</v>
+        <v>0.3193622275919891</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6628368293392736</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.161308839829331</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6153690958744571</v>
+        <v>-0.5858440155454991</v>
       </c>
       <c r="M6" t="n">
-        <v>0.720514281717389</v>
+        <v>-0.174695132839171</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1967853069301546</v>
+        <v>0.7908629256539699</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5069857905825147</v>
+        <v>0.9393209211457316</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9112543269379719</v>
+        <v>0.3465795990479323</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9281072915942485</v>
+        <v>0.4802563142690392</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-1.7825248270718</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2724646145738592</v>
+        <v>-0.6289646691017665</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2730575346845301</v>
+        <v>-0.8350007290074379</v>
       </c>
       <c r="U6" t="n">
-        <v>0.115577714834023</v>
+        <v>0.7827246749063416</v>
       </c>
       <c r="V6" t="n">
+        <v>0.2223038438657806</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.1535225464049944</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-1.180540638197231</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.8206664070150588</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.610745234664009</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-0.8838458304440689</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-0.303960741518821</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.1084016239925458</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-0.3038884130792998</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.2369450320097328</v>
+      </c>
+      <c r="AI6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>htYUpyrn</t>
+          <t>0n3Ddmal</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.505745958599491</v>
+        <v>1.568324270223589</v>
       </c>
       <c r="C7" t="n">
-        <v>1.425283213108217</v>
+        <v>-1.451354473291761</v>
       </c>
       <c r="D7" t="n">
-        <v>1.696871791219498</v>
+        <v>1.633539779427207</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.325675397157449</v>
+        <v>1.624998815055351</v>
       </c>
       <c r="F7" t="n">
-        <v>2.704064827579225</v>
+        <v>-0.679560351381822</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.183903199042094</v>
+        <v>-0.1731686280403403</v>
       </c>
       <c r="H7" t="n">
-        <v>2.271364698150517</v>
+        <v>-0.1404070909990901</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6913308343796587</v>
+        <v>0.8440647867440862</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01539982324817748</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5570523483047296</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1888828161507944</v>
+        <v>0.5626665281726493</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4810652780168685</v>
+        <v>-0.3002207773839639</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1946407470405924</v>
+        <v>1.779923778229429</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1896759637498451</v>
+        <v>-0.9281082915579664</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9055747676008451</v>
+        <v>-0.3661306835115803</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.01591852713794537</v>
+        <v>-2.522146694377557</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.2727800297853217</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2523641513343919</v>
+        <v>1.320116706985648</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6378575972984013</v>
+        <v>-0.4094318579966947</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3986970721605224</v>
+        <v>-0.0472905475096699</v>
       </c>
       <c r="V7" t="n">
+        <v>1.649332423143475</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.9479595835726981</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0.2583641835105765</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-0.3895269803479636</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.810809413338624</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-0.09403752466641761</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-0.03993566843525989</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.01866942981561715</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-0.08280661527951066</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-0.09107459714580574</v>
+      </c>
+      <c r="AI7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dKkDSgSH</t>
+          <t>SM4QZAZp</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.505745958599491</v>
+        <v>1.548609129611189</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2003886725650971</v>
+        <v>1.393762108546903</v>
       </c>
       <c r="D8" t="n">
-        <v>1.680025094724479</v>
+        <v>1.64964691859188</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8618767801220406</v>
+        <v>1.607989243553732</v>
       </c>
       <c r="F8" t="n">
-        <v>3.594870669747482</v>
+        <v>-0.679560351381822</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.267125234905288</v>
+        <v>-0.1731686280403403</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5486890642581389</v>
+        <v>-0.1404070909990901</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6913308343796587</v>
+        <v>0.5018674655579358</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01539982324817748</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2005509057437071</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.084619465924596</v>
+        <v>-0.4169454061751829</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.132858400438903</v>
+        <v>-0.3316021885201621</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8946633614712054</v>
+        <v>0.1108835895083416</v>
       </c>
       <c r="O8" t="n">
-        <v>1.757425907566879</v>
+        <v>-2.173061100027099</v>
       </c>
       <c r="P8" t="n">
-        <v>1.696035790638628</v>
+        <v>-0.4679464381629391</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.7788760079382698</v>
+        <v>1.218942768777329</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.04441282346786362</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8803364960602643</v>
+        <v>0.1930872536192972</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9604560837780212</v>
+        <v>-0.1167708393534231</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7979003745912392</v>
+        <v>0.4156087489555035</v>
       </c>
       <c r="V8" t="n">
+        <v>-0.1549254927897555</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.05290597506377909</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.6697753892298235</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-1.055569561734831</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.3020513928072782</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-0.9021225105987172</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.7359309071357077</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.01866942981561715</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-0.5780844002945489</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0.8420256960418482</v>
+      </c>
+      <c r="AI8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>A3m1Vera</t>
+          <t>QDIbviRT</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.486114019161555</v>
+        <v>1.686615113897985</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.179384449020297</v>
+        <v>-1.035270230097964</v>
       </c>
       <c r="D9" t="n">
-        <v>1.831645363179644</v>
+        <v>1.762396892744593</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3345666991006706</v>
+        <v>1.659017958058589</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.749964383262056</v>
+        <v>-0.679560351381822</v>
       </c>
       <c r="G9" t="n">
-        <v>2.607373926479085</v>
+        <v>-0.1731686280403403</v>
       </c>
       <c r="H9" t="n">
-        <v>0.40515264949773</v>
+        <v>-0.2409738189422453</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.843293104417182</v>
+        <v>-2.372590032405727</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6628368293392736</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1.581956307061404</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.565848628267925</v>
+        <v>1.153811660968755</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4959846044519273</v>
+        <v>2.99482739191686</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.04145036600554177</v>
+        <v>0.3581488026522068</v>
       </c>
       <c r="O9" t="n">
-        <v>1.739677370410409</v>
+        <v>0.5658350786049919</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3455987451956497</v>
+        <v>0.265126995326845</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1544842240974258</v>
+        <v>-2.557889587337636</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-1.668341223913071</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5006047552454505</v>
+        <v>-1.348880506419148</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6443678966268347</v>
+        <v>-2.024389426274485</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.107904949215873</v>
+        <v>1.909599859323447</v>
       </c>
       <c r="V9" t="n">
+        <v>0.4665971360360476</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.2598645120101195</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0.2018223208730525</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-0.3549489534903147</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.476802957650956</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0.4803862357133053</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.932515641442911</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.3749557953071793</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.3853621185222921</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.4021850158195144</v>
+      </c>
+      <c r="AI9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>8lOY3V6E</t>
+          <t>ImJfuXBN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.486114019161555</v>
+        <v>1.548609129611189</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.397984150381743</v>
+        <v>1.011414425612062</v>
       </c>
       <c r="D10" t="n">
-        <v>1.646331701734443</v>
+        <v>1.617432640262533</v>
       </c>
       <c r="E10" t="n">
-        <v>1.460098519733396</v>
+        <v>1.607989243553732</v>
       </c>
       <c r="F10" t="n">
-        <v>1.961726625772345</v>
+        <v>-0.679560351381822</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.537930743871087</v>
+        <v>-0.1731686280403403</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.585473535731909</v>
+        <v>0.46299327665984</v>
       </c>
       <c r="I10" t="n">
-        <v>2.719029985417131</v>
+        <v>-1.733821699524914</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6628368293392736</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.161308839829331</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.285589968912503</v>
+        <v>0.4275476406763966</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8487815870117064</v>
+        <v>1.394375423970746</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1700084523884368</v>
+        <v>1.779923778229429</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4934744920220367</v>
+        <v>2.05977844876795</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3249233483110439</v>
+        <v>-0.2643149288602215</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1466464352598</v>
+        <v>-0.6873448557601923</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.7295144424202374</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2925316937936701</v>
+        <v>-1.629770692921382</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1997216390533094</v>
+        <v>-2.459170478689559</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5363559905488536</v>
+        <v>0.4362237950067862</v>
       </c>
       <c r="V10" t="n">
+        <v>-0.3784596955406523</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.1535225464049944</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.2047574576196823</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-1.018489715573157</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.1114509683005457</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-0.01739580829774839</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.6564446588559724</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.17610201175713</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.246222321321218</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.4879397388453834</v>
+      </c>
+      <c r="AI10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ITj9TZCB</t>
+          <t>dYUosgsB</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.505745958599491</v>
+        <v>1.548609129611189</v>
       </c>
       <c r="C11" t="n">
-        <v>1.218706122663541</v>
+        <v>-0.9453060694074138</v>
       </c>
       <c r="D11" t="n">
-        <v>1.663178398229461</v>
+        <v>1.746289753579919</v>
       </c>
       <c r="E11" t="n">
-        <v>1.559802143001956</v>
+        <v>1.64200838655697</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.046899663984808</v>
+        <v>-0.679560351381822</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6214668607298952</v>
+        <v>-0.1731686280403403</v>
       </c>
       <c r="H11" t="n">
-        <v>1.524879878689402</v>
+        <v>1.46866055609139</v>
       </c>
       <c r="I11" t="n">
-        <v>2.04313026840464</v>
+        <v>0.3193622275919891</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8689534219393596</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.004346539335786886</v>
+        <v>0.7653448594170287</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3572948536840305</v>
+        <v>-0.01778807715817907</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.133592168243821</v>
+        <v>-1.249075082782914</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6614544481034287</v>
+        <v>-2.733289863838208</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3434654390881352</v>
+        <v>0.8556583723047267</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.809228912406108</v>
+        <v>0.7423708626429487</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>-2.239259239706715</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3243115565055278</v>
+        <v>0.3458401781347056</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3594874943053419</v>
+        <v>0.8099670743973927</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2165299199474796</v>
+        <v>1.084357354889244</v>
       </c>
       <c r="V11" t="n">
+        <v>-1.54961661589391</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-2.051509387465994</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-1.778836245584099</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-1.516779606147276</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.142361884068474</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-2.803743389281955</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0.5250957139859751</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.368624987105641</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-0.5920929084253582</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-1.768875950480877</v>
+      </c>
+      <c r="AI11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>lfn5UFc5</t>
+          <t>U3Cs29yR</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.505745958599491</v>
+        <v>1.548609129611189</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9223129059385726</v>
+        <v>1.112624106388932</v>
       </c>
       <c r="D12" t="n">
-        <v>1.663178398229461</v>
+        <v>1.633539779427207</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4132104754135239</v>
+        <v>1.607989243553732</v>
       </c>
       <c r="F12" t="n">
-        <v>1.813258985410969</v>
+        <v>-0.679560351381822</v>
       </c>
       <c r="G12" t="n">
-        <v>1.253346381650092</v>
+        <v>-0.1731686280403403</v>
       </c>
       <c r="H12" t="n">
-        <v>1.151637468958845</v>
+        <v>1.292668782190869</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6913308343796587</v>
+        <v>1.254701572167467</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.279474188934014</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5124519793783373</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4260565516477354</v>
+        <v>0.5626665281726493</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2786234786363694</v>
+        <v>0.6412215567019861</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1761936587845546</v>
+        <v>-1.496340295926779</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.370258583002284</v>
+        <v>0.6280827190284484</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.0449161920536345</v>
+        <v>-1.649009192118703</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.5938300534444186</v>
+        <v>0.07517019405481555</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.328084886642443</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.09347075029184576</v>
+        <v>-2.184977166345921</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9850303157760573</v>
+        <v>-0.5348983777369238</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.573965285557133</v>
+        <v>1.010785770894327</v>
       </c>
       <c r="V12" t="n">
+        <v>0.6787442370883306</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.06489551040161282</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0.4377585636929838</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.6221221263981437</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.1791100678655</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.4610252394863712</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.1013763533249538</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.1009162315578909</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-0.06708679584224624</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.360301489714998</v>
+      </c>
+      <c r="AI12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>vquIRDsO</t>
+          <t>vcKjtDdH</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.682433413540919</v>
+        <v>1.568324270223589</v>
       </c>
       <c r="C13" t="n">
-        <v>1.164816446895365</v>
+        <v>1.202588267079483</v>
       </c>
       <c r="D13" t="n">
-        <v>1.646331701734443</v>
+        <v>1.60132550109786</v>
       </c>
       <c r="E13" t="n">
-        <v>1.609653954636235</v>
+        <v>1.64200838655697</v>
       </c>
       <c r="F13" t="n">
-        <v>1.763769771957177</v>
+        <v>-0.679560351381822</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8020038667070943</v>
+        <v>-0.1731686280403403</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.585473535731909</v>
+        <v>0.5635600046029947</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8294435288984455</v>
+        <v>-0.5931639622377454</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6628368293392736</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5570523483047296</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.9290150771812437</v>
+        <v>0.005301117250606866</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8656454365765585</v>
+        <v>-0.01778807715817907</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5823700872144754</v>
+        <v>0.6054140157960713</v>
       </c>
       <c r="O13" t="n">
-        <v>0.05194646981657778</v>
+        <v>1.624044965803754</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1661914884875794</v>
+        <v>0.55021110835065</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.1913241854915561</v>
+        <v>-1.020945190054259</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>0.04441282346786362</v>
       </c>
       <c r="S13" t="n">
-        <v>1.600433213550304</v>
+        <v>-0.144691957658752</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4335319194785925</v>
+        <v>-1.389003233400881</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3309400124134132</v>
+        <v>-0.7560155003343036</v>
       </c>
       <c r="V13" t="n">
+        <v>-0.425408435777359</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.6138077152163057</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.5925019723462719</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-1.178265983311031</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-1.715421623158845</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.3401898085187953</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-0.4106486966291439</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.06512311747472022</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.1532278675305467</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-2.25774585395496</v>
+      </c>
+      <c r="AI13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>jDDw3kMK</t>
+          <t>Me49cTqr</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.505745958599491</v>
+        <v>1.548609129611189</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.6764141418506531</v>
+        <v>1.472480749151134</v>
       </c>
       <c r="D14" t="n">
-        <v>1.663178398229461</v>
+        <v>1.665754057756553</v>
       </c>
       <c r="E14" t="n">
-        <v>1.160987649927718</v>
+        <v>1.744065815566682</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.749964383262056</v>
+        <v>-0.679560351381822</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.267125234905288</v>
+        <v>-0.1731686280403403</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2169180333865322</v>
+        <v>-1.724333056103782</v>
       </c>
       <c r="I14" t="n">
-        <v>2.212105197657763</v>
+        <v>-0.2737797957973386</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01539982324817748</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.091804512146263</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.9213265217452242</v>
+        <v>-0.5520642936714356</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0260236731337764</v>
+        <v>-1.524095811695699</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2126014255865129</v>
+        <v>2.027188991373294</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2691974268746732</v>
+        <v>-0.3367557075351285</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2277026561284581</v>
+        <v>-0.5493990418840262</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2683019140112201</v>
+        <v>1.874229139712102</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>-0.6406887954845102</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5273482844407906</v>
+        <v>-1.555761454347699</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8716722260055587</v>
+        <v>-0.6314962946468141</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2031602493867335</v>
+        <v>-0.06389966314111102</v>
       </c>
       <c r="V14" t="n">
+        <v>-0.09030522760141546</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.285751709612508</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.9755927495174846</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.5939433280726443</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.7873973251262817</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-1.00241861342269</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-0.6036594194074488</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.153069876691116</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-0.2017920607915613</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-0.3022079695786887</v>
+      </c>
+      <c r="AI14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>trWntSE7</t>
+          <t>rVQsrZR4</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.505745958599491</v>
+        <v>1.666899973285585</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.305127025812708</v>
+        <v>-1.282671671996979</v>
       </c>
       <c r="D15" t="n">
-        <v>1.696871791219498</v>
+        <v>1.60132550109786</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.231899308517704</v>
+        <v>1.607989243553732</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.255072248724135</v>
+        <v>-0.679560351381822</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.537930743871087</v>
+        <v>-0.1731686280403403</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1977957552029758</v>
+        <v>0.3624265487166848</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8603057636327814</v>
+        <v>0.8395021557949378</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.279474188934014</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.02230018446319613</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.270502992207852</v>
+        <v>0.5119969453615547</v>
       </c>
       <c r="M15" t="n">
-        <v>1.209748613354146</v>
+        <v>-1.461332989423302</v>
       </c>
       <c r="N15" t="n">
-        <v>1.016243205691512</v>
+        <v>0.1479733714799218</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1417832973186906</v>
+        <v>0.2047987641489437</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3219736874487772</v>
+        <v>0.55021110835065</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2947494481333916</v>
+        <v>-0.1297557255829675</v>
       </c>
       <c r="R15" t="n">
-        <v>1.061404349769643</v>
+        <v>-0.09260750032261125</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6645508261711883</v>
+        <v>0.8727229158899278</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3144783620208266</v>
+        <v>-1.33601906121329</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6660188663420447</v>
+        <v>-0.6902586157153486</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.4245322947440672</v>
+        <v>-0.5077568247602878</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.5394962212869037</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.815419083451798</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.4853877056313386</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0.548825731161159</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.339223278801569</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.7559718884763029</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.5618251933765732</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.418617261526828</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.9839047669522736</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>AoWGqXpJ</t>
+          <t>l8RwqFCb</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.505745958599491</v>
+        <v>1.568324270223589</v>
       </c>
       <c r="C16" t="n">
-        <v>1.182779672151424</v>
+        <v>-0.1581196633650958</v>
       </c>
       <c r="D16" t="n">
-        <v>1.646331701734443</v>
+        <v>1.681861196921226</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.381454743420543</v>
+        <v>1.693037101061826</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8591585410937995</v>
+        <v>-0.679560351381822</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9825408726842934</v>
+        <v>-0.1731686280403403</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.461059399155056</v>
+        <v>1.388207173736866</v>
       </c>
       <c r="I16" t="n">
-        <v>2.719029985417131</v>
+        <v>-1.496564890169183</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.161308839829331</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9121763491218614</v>
+        <v>-0.501394710860341</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.502244679959345</v>
+        <v>-1.806528511921484</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.132698390401482</v>
+        <v>-0.717454874523605</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.857832296685331</v>
+        <v>-1.992542942799074</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.01311401317092</v>
+        <v>-0.3661306835115803</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.625332776615377</v>
+        <v>-1.828734570952033</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6477407742304916</v>
+        <v>1.757166870848798</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8070128741975213</v>
+        <v>-1.272996266259773</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7049692883607892</v>
+        <v>-0.147591143601905</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.31417565046972</v>
+        <v>0.1055766594264327</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8796239356685686</v>
+        <v>-1.275916321436542</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-1.791909883194658</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-1.315877689501947</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.1900146597462184</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-1.252881248269476</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-0.1743270557984635</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-0.573074869113269</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.4041108871695768</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-0.04882968699266621</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-0.9036758638525262</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>SvbdWyTh</t>
+          <t>foKU4Bi8</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.682433413540919</v>
+        <v>1.568324270223589</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.4878002766620366</v>
+        <v>-0.6866591074220807</v>
       </c>
       <c r="D17" t="n">
-        <v>1.713718487714516</v>
+        <v>1.633539779427207</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5627659103163628</v>
+        <v>1.659017958058589</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.749964383262056</v>
+        <v>-0.679560351381822</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.99631972593949</v>
+        <v>-0.1731686280403403</v>
       </c>
       <c r="H17" t="n">
-        <v>1.89812228841996</v>
+        <v>1.493802238077179</v>
       </c>
       <c r="I17" t="n">
-        <v>2.719029985417131</v>
+        <v>-2.167271639694037</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01539982324817748</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.230813167512397</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-3.066433488396978</v>
+        <v>0.005301117250606866</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3484385717521059</v>
+        <v>0.9236542569277709</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4508570618426563</v>
+        <v>-0.9399935663530832</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3395886254272084</v>
+        <v>-2.14193727981537</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.09252426296778681</v>
+        <v>-1.587919739327887</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.5309113914638595</v>
+        <v>-0.3775731167728454</v>
       </c>
       <c r="R17" t="n">
-        <v>1.268236137539219</v>
+        <v>1.072065251896424</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1118241078406951</v>
+        <v>-1.86276037707678</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7854978474796603</v>
+        <v>-1.967872975941053</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5457741986610256</v>
+        <v>-0.2829259046405856</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.7573605097485532</v>
+        <v>-0.7888871811195466</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.05290597506377909</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.08886632804918487</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-0.3888017602108453</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.441706979482377</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0.09576741620368558</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-0.06101402247696378</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0.01866942981561715</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-0.04679338610317681</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-0.226067875748242</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hIoLKAg0</t>
+          <t>AHSZqech</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.486114019161555</v>
+        <v>1.548609129611189</v>
       </c>
       <c r="C18" t="n">
-        <v>-1.206329286904385</v>
+        <v>0.6628033029361787</v>
       </c>
       <c r="D18" t="n">
-        <v>1.781105273694589</v>
+        <v>1.64964691859188</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.054454200483318</v>
+        <v>1.744065815566682</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.675730563081368</v>
+        <v>-0.679560351381822</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4409298547526964</v>
+        <v>-0.1731686280403403</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7161879909398612</v>
+        <v>-1.749474738089571</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4378684404999746</v>
+        <v>1.231888417421724</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6320371828429185</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5124519793783373</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.09749055342066222</v>
+        <v>0.005301117250606866</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5558557338551776</v>
+        <v>-1.900672745330079</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2270825517488297</v>
+        <v>-0.2600142302074548</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5376586831843403</v>
+        <v>-1.986318178756729</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.907230799814482</v>
+        <v>-0.4679464381629391</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.4773065511213163</v>
+        <v>1.409571531231081</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.5011472361027791</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3654042086373105</v>
+        <v>-2.032453945476422</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4152971284087136</v>
+        <v>0.9732430994106843</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4077168485667712</v>
+        <v>-1.609387336032737</v>
       </c>
       <c r="V18" t="n">
-        <v>0.4381040992471517</v>
+        <v>0.8656921670750777</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.05290597506377909</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-0.4586433222108385</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.3101645691483128</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-1.102924093880922</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-0.8581418985804821</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-2.735165944259874</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-0.01866942981561715</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-0.7120210916620433</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-1.788590796204836</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>KEflYcbt</t>
+          <t>xUcLQXdU</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.525377898037428</v>
+        <v>1.666899973285585</v>
       </c>
       <c r="C19" t="n">
-        <v>-1.269200575300591</v>
+        <v>0.02180865801600549</v>
       </c>
       <c r="D19" t="n">
-        <v>1.646331701734443</v>
+        <v>1.665754057756553</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.580861989957662</v>
+        <v>1.607989243553732</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1168203392869193</v>
+        <v>-0.679560351381822</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.544977210996492</v>
+        <v>-0.1731686280403403</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3413321699633847</v>
+        <v>-1.025394296898854</v>
       </c>
       <c r="I19" t="n">
-        <v>1.029280692885904</v>
+        <v>1.815905178912753</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6320371828429185</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.270055233426774</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1392698735258687</v>
+        <v>0.005301117250606866</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.007179991156510987</v>
+        <v>-1.147518878061319</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0517622518599371</v>
+        <v>1.17412400602696</v>
       </c>
       <c r="O19" t="n">
-        <v>0.738992713748828</v>
+        <v>-0.9654568758120402</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6756813702004395</v>
+        <v>0.9167478250955421</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.5666359625008918</v>
+        <v>0.03704444156406628</v>
       </c>
       <c r="R19" t="n">
-        <v>0.23407719869134</v>
+        <v>-0.2296278241130858</v>
       </c>
       <c r="S19" t="n">
-        <v>0.271512508361441</v>
+        <v>0.3697867832185063</v>
       </c>
       <c r="T19" t="n">
-        <v>1.059388828608515</v>
+        <v>-0.8070250860923833</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.21164269749548</v>
+        <v>0.753101455684154</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3566081692329476</v>
+        <v>0.9786068587836488</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.4162497555470699</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-1.001262225025833</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-0.1192794060547911</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.595645082886843</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-0.5626500995780993</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.2853042402123743</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.07106276436131152</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-0.1489396123922238</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.021697335391437</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>EyfhXHDn</t>
+          <t>EkZQoHSu</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.603905655789173</v>
+        <v>1.745760535735183</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.9189176828074458</v>
+        <v>-1.451354473291761</v>
       </c>
       <c r="D20" t="n">
-        <v>1.747411880704552</v>
+        <v>1.633539779427207</v>
       </c>
       <c r="E20" t="n">
-        <v>0.06424779397356667</v>
+        <v>1.607989243553732</v>
       </c>
       <c r="F20" t="n">
-        <v>0.922453143242713</v>
+        <v>-0.679560351381822</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6422921811104975</v>
+        <v>-0.1731686280403403</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5486890642581387</v>
+        <v>-0.648269067112023</v>
       </c>
       <c r="I20" t="n">
-        <v>0.522355905126536</v>
+        <v>-0.7711065692545437</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.495286524297713</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3788016270242184</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3712211940096389</v>
+        <v>0.5119969453615547</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2116300340794384</v>
+        <v>0.9236542569277709</v>
       </c>
       <c r="N20" t="n">
-        <v>1.62976306471112</v>
+        <v>-0.3465570548078079</v>
       </c>
       <c r="O20" t="n">
-        <v>1.145919073730525</v>
+        <v>0.2857206966994373</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3026440947467898</v>
+        <v>-1.221383022582995</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.28489772099319</v>
+        <v>-0.8064878322937878</v>
       </c>
       <c r="R20" t="n">
-        <v>-1.558464961978317</v>
+        <v>0.2499433091535757</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1631020661870673</v>
+        <v>1.857577297633989</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3183478908927143</v>
+        <v>-0.05309563864441008</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4452169146510656</v>
+        <v>-0.4061402942814327</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.001887361588584</v>
+        <v>0.801673020632674</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.9479595835726981</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-0.4058805942592831</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-0.5549722260000983</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.9621994967013123</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-0.2183640773233486</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>-0.2535823521918567</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>-0.01866942981561715</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-0.2340154755167278</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0.7366769943537093</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>htYUpyrn</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.568324270223589</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-1.338899272428573</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.633539779427207</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.659017958058589</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.679560351381822</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.1731686280403403</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.0003863281213269582</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.733777821828077</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.5119969453615547</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.5470773232933906</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-1.181077149168351</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.5284864943509182</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.4272201363023957</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.8805767154219183</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-0.2296278241130858</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.4069987738523333</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.1955767428226758</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.6160264024465802</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.6478549306209227</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.9010440105116134</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-0.05681648317214469</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.296510604273168</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.04180419721895196</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.2551749278357876</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>-0.4571756221278668</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>-0.01866942981561715</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>-0.1362020022503364</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0.7091344808201406</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>vquIRDsO</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.588039410835988</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.011414425612062</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.617432640262533</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.77808495856992</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.679560351381822</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.1731686280403403</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.3171715211422649</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-1.920889568440009</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.501394710860341</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.959230411244129</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.8217710772969532</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.2857206966994373</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.7937568530472879</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-0.2631958593005946</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-0.02409733842737382</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-1.946889337383207</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-1.50579447801491</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.1189957133744388</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-0.6021031926089796</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-0.2191956173580683</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.1772652463941598</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-0.1046435071476192</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>-0.1736961898754502</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.5014462984244167</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0.3837836355721076</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.733488465473509</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.665872412962373</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0.8030535455399074</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>lfn5UFc5</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.548609129611189</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-1.181461991220109</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.60132550109786</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.744065815566682</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.679560351381822</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.1731686280403403</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1512364200360595</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.8258581406443275</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.501394710860341</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.806528511921484</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.398086811089091</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.414589999181653</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.9778372778863575</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-0.2060072305644681</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-0.1611176622178484</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-1.398759012383375</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.7592686855606355</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.06144023320224846</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.2541358138211322</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-0.05290597506377909</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-1.271476125559577</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.3530923646381275</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>-0.6188746211099471</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.2252026766356677</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>-1.041225935623095</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-0.01866942981561715</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.0529271904553387</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>-0.2108398569821657</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>dKkDSgSH</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1.568324270223589</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-1.586300714327587</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.665754057756553</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.64200838655697</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.679560351381822</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.1731686280403403</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.4672489568143441</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.4334280013207057</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.501394710860341</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.01778807715817907</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.5435977125101054</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.62000721257906</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.9770252114197339</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-0.2346015449325314</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.3869636329440505</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.1115572067394411</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-3.091702590821322</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.6723195353414863</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.1279965097019052</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.758035145094095</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.762706189646104</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.06072433581908171</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>-0.8248448932811251</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9196225066679106</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.9915684364857092</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>-0.3139411323013466</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.9183849485204486</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>-0.1424303134947043</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>ITj9TZCB</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1.568324270223589</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.5067307860409794</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.665754057756553</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.624998815055351</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.679560351381822</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.1731686280403403</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.1655487729848791</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.8669218191866657</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.005301117250606866</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.394375423970746</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.450873257581156</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.3790921573346222</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.9770252114197339</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.230857066430688</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.414616061372611</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-3.007545922270248</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.05931244818109239</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.21897870024955</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.3290092521646335</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.3505679532615525</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-0.7703791296339561</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.9269916239611559</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.914665111319095</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>-1.206903075029481</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>-0.3306025914651046</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>-0.4869692431009714</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>-0.3246329204689358</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.3820234297491032</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>jDDw3kMK</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1.568324270223589</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.472480749151134</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.665754057756553</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.624998815055351</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.679560351381822</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.1731686280403403</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1.598624646174838</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.688195390033427</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.005301117250606866</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.766747201246779</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.6363221674390546</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.08776514584130231</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.3661306835115803</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.19511417347061</v>
+      </c>
+      <c r="R26" t="n">
+        <v>-0.2981379860083233</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.7937770350262913</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-1.063892352857831</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-1.604843480486192</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.1432036772439577</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.2306725998832221</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.2722088573230936</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.622345161717154</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>-0.2895890591804445</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.2165156126115418</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>-0.8811300410560468</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.00439186231208711</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0.5542994936962837</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>-0.03113369674765353</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>8lOY3V6E</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1.548609129611189</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.6178212225909034</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.60132550109786</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.607989243553732</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.679560351381822</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.1731686280403403</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1.372349508302739</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-1.961953246982347</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.005301117250606866</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.01778807715817907</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.305362356160142</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.24652137003832</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.161105636258803</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-1.378374119655044</v>
+      </c>
+      <c r="R27" t="n">
+        <v>-0.2981379860083233</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-1.300273574208949</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-1.834494153154156</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.6915558375570044</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-0.3975588775138771</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.3318017240371173</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.4968278399862239</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-1.580880135225062</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>-1.210393766941126</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>-0.1778996578863155</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0.2139884881589325</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.506190918210278</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>-0.2913558708474883</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>-0.8882536101531965</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>A3m1Vera</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1.548609129611189</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.9453060694074138</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.746289753579919</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.795094530071538</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.679560351381822</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.1731686280403403</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.041251962332981</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.3649885370834756</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.005301117250606866</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-0.01778807715817907</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-1.032718021282032</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-2.14193727981537</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-2.504261531190118</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.659771781951631</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.757166870848798</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-0.9014506190362108</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.9308557616606022</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-0.4588623697066908</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-1.395798525882159</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-0.2405682673081196</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.74482406100386</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-1.324836807735342</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0.03347956222635174</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>-0.1480402256994958</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0.8745086975527017</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>-0.01866942981561715</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0.7832985335342877</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>-0.4105910623271173</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/usa/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/usa/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI15"/>
+  <dimension ref="A1:AU13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,1694 +436,1968 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>id_team_home</t>
+          <t>id_team_away</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_home</t>
+          <t>id_coach_away</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_away</t>
+          <t>id_competition</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>id_competition</t>
+          <t>is_cup</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>is_cup</t>
+          <t>dif_mean_last_360_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goal_attempts</t>
+          <t>dif_mean_last_360_matches_shots_on_goal_against</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
+          <t>dif_mean_last_60_matches_goal_attempts</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
+          <t>dif_mean_last_60_matches_goal_attempts_against</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+          <t>dif_mean_last_360_matches_goal_attempts</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
+          <t>dif_mean_last_360_matches_goal_attempts_against</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
+          <t>dif_mean_last_360_matches_goals_against</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_fouls</t>
+          <t>dif_mean_last_360_matches_points</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_fouls_against</t>
+          <t>dif_mean_last_360_matches_points_against</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_points_against</t>
+          <t>dif_mean_last_60_matches_goal_ratio</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
+          <t>dif_mean_last_60_matches_goal_ratio_against</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goals</t>
+          <t>dif_mean_last_360_matches_goal_ratio</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_home_against</t>
+          <t>dif_mean_last_60_matches_PPS_against</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_away_against</t>
+          <t>dif_mean_last_360_matches_PPS</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_age_player_sub</t>
+          <t>dif_mean_last_360_matches_attacks</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_hei_player_start</t>
+          <t>dif_mean_last_60_matches_dangerous_attacks</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_hei_player_miss</t>
+          <t>dif_mean_last_60_matches_dangerous_attacks_against</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_int_rep_player_start</t>
+          <t>dif_mean_last_360_matches_dangerous_attacks_against</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_360_matches_dead_balls</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_dead_balls_against</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_yellow_cards</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_yellow_cards_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_yellow_cards</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_red_cards_against</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_defensive_actions</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_defensive_actions_against</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_PPDA</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_PPDA_against</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_PPDA</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_KGP</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_clean_sheet_against</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_clean_sheet_against</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_360_matches_mean_rat_player_start_away_against</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
           <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rVQsrZR4</t>
+          <t>Kz477keG</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.568324270223589</v>
+        <v>1.627304721194861</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.282671671996979</v>
+        <v>-1.273494690448302</v>
       </c>
       <c r="D2" t="n">
-        <v>1.60132550109786</v>
+        <v>1.691539342043302</v>
       </c>
       <c r="E2" t="n">
-        <v>1.607989243553732</v>
+        <v>-0.2516569535949728</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.679560351381822</v>
+        <v>-0.2516569535947502</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1731686280403403</v>
+        <v>-1.736925750478082</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3624265487166848</v>
+        <v>-0.459252962573645</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8395021557949378</v>
+        <v>-4.760711150012864</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0.7248769228829627</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-1.258165895212692</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5119969453615547</v>
+        <v>0.8874034089071657</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.994816978738674</v>
+        <v>-0.5794543984791194</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1479733714799218</v>
+        <v>-0.6566194999040601</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2047987641489437</v>
+        <v>1.423834836769957</v>
       </c>
       <c r="P2" t="n">
-        <v>0.55021110835065</v>
+        <v>2.857142785188833</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1297557255829675</v>
+        <v>-0.8575818249925836</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.09260750032261125</v>
+        <v>2.160502142878789</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8727229158899278</v>
+        <v>0.2246774835314991</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.33601906121329</v>
+        <v>-1.547274165227749</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6336366354932768</v>
+        <v>-0.4630832862497295</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.4601503669346664</v>
+        <v>-1.304386774728571</v>
       </c>
       <c r="W2" t="n">
-        <v>-1.054135761566998</v>
+        <v>1.579807641491311</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6260666239591424</v>
+        <v>1.049037240584286</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1638136810830087</v>
+        <v>-0.6302031019669018</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.937546713849095</v>
+        <v>-1.360967283167446</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.478806959569356</v>
+        <v>-2.002071887148178</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5889400194433834</v>
+        <v>-1.632068613764654</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.5441007480548299</v>
+        <v>-0.5101769171800056</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.245634982629502</v>
+        <v>-0.351370276592837</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.9069793023219886</v>
+        <v>-2.731543404967539</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.5143664249112582</v>
+        <v>0.7693880912438136</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.554592753585821</v>
+        <v>3.153466340643142</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.9136379675317353</v>
+        <v>-0.8892904958489537</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.629260584129833</v>
+        <v>1.931173419576069</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-0.5756621832978706</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.3946341266333761</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.075751488463705</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-0.006536957239599399</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.3341566482384736</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>-0.1430987407700007</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.7843594032959015</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-0.6204838874312193</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.7569875438021191</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.5949106925055023</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.4611731295092106</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.4602988085585026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>l8RwqFCb</t>
+          <t>zJAPgoq7</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.568324270223589</v>
+        <v>1.509631310229416</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1581196633650958</v>
+        <v>-0.6342377002189306</v>
       </c>
       <c r="D3" t="n">
-        <v>1.681861196921226</v>
+        <v>1.657810658347641</v>
       </c>
       <c r="E3" t="n">
-        <v>1.693037101061826</v>
+        <v>-0.2516569535949728</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.679560351381822</v>
+        <v>-0.2516569535947502</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1731686280403403</v>
+        <v>1.594772308623398</v>
       </c>
       <c r="H3" t="n">
-        <v>1.388207173736866</v>
+        <v>1.615453391497765</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.496564890169183</v>
+        <v>0.6013037961274265</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2.381924266296041</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.8733226096479751</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.501394710860341</v>
+        <v>1.633848883356718</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.488509244201154</v>
+        <v>2.165687108015928</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.717454874523605</v>
+        <v>-0.257460055948077</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.992542942799074</v>
+        <v>0.2978866100581311</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3661306835115803</v>
+        <v>1.899395610297512</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.828734570952033</v>
+        <v>-1.435528444315844</v>
       </c>
       <c r="R3" t="n">
-        <v>1.757166870848798</v>
+        <v>-0.9627021891301512</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.272996266259773</v>
+        <v>0.4105222223739407</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.147591143601905</v>
+        <v>0.1121369715426597</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08039443586760814</v>
+        <v>0.6914730880947857</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.373481992439204</v>
+        <v>1.988288959685559</v>
       </c>
       <c r="W3" t="n">
-        <v>-2.544629016781424</v>
+        <v>0.4159450727662533</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.748903941221997</v>
+        <v>-0.3764794645056244</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.3562604879868753</v>
+        <v>-0.1897599197159128</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1.295012117800582</v>
+        <v>-0.8885335880839144</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.09162948971274651</v>
+        <v>1.153314037709097</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.5500770272032856</v>
+        <v>-1.632068613764654</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1.165267876708017</v>
+        <v>0.3855041425575755</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.204731779882899</v>
+        <v>-1.077347689947205</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.4908458301031332</v>
+        <v>-0.09784362865046625</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.507633502767381</v>
+        <v>0.5822131351521155</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.1504927939324729</v>
+        <v>-0.7698531147526216</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.9289069816805153</v>
+        <v>1.777390314706113</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.2265778389578908</v>
+        <v>-0.2626058983090887</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.642779755129289</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.3946341266333761</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-0.589161776331411</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-0.7370667898635007</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.262241308066626</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.3735028596140627</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.3268929031676678</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.9023475351224602</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.080622093425624</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0.5262990966270383</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.4611731295092106</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.2085126830997785</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>foKU4Bi8</t>
+          <t>tdBLfRT0</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.548609129611189</v>
+        <v>1.490019075068509</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.6866591074220807</v>
+        <v>1.490616520825179</v>
       </c>
       <c r="D4" t="n">
-        <v>1.633539779427207</v>
+        <v>1.657810658347641</v>
       </c>
       <c r="E4" t="n">
-        <v>1.659017958058589</v>
+        <v>-0.2516569535949728</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.679560351381822</v>
+        <v>-0.2516569535947502</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1731686280403403</v>
+        <v>1.21087294378866</v>
       </c>
       <c r="H4" t="n">
-        <v>1.493802238077179</v>
+        <v>0.2379404111235494</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.167271639694037</v>
+        <v>-0.03703131650832238</v>
       </c>
       <c r="J4" t="n">
+        <v>0.02075536251999814</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.8266747637320989</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.1787032156416357</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0.2133752710077678</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.7775146287757358</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.9191788141910679</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.7685471099258061</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-2.776478482253063</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-1.707828456193103</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-0.375852880156183</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.8597176047403037</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.6120862388681664</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0.1948982120455491</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-2.399851464471789</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.5937649043906937</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.9083738159492073</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0.2719881414388846</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-1.551302469311425</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-0.2630959778203125</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-3.37231564190536</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.25361090120247</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-2.646585347666988</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-0.3026139300086442</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.439112920508937</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.794168261626826</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.8145801409566152</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.011982950130581</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.3946341266333761</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-1.246905288349235</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-1.335518019400521</v>
+      </c>
+      <c r="AN4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
+      <c r="AO4" t="n">
+        <v>-1.400553014080995</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-0.1617939260657689</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-1.217766578198519</v>
+      </c>
+      <c r="AR4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
-        <v>0.005301117250606866</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.237468368289754</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-0.9399935663530832</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-2.14193727981537</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-1.587919739327887</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-0.3775731167728454</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.072065251896424</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-1.86276037707678</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-1.967872975941053</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-0.2038517822270811</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-0.7081460041083228</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.554227435058249</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-0.05290597506377909</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-0.5859036275761746</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.1237898195593917</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-0.2670431994018544</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-0.2593835825976086</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-0.4716392736087734</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-0.121245710040672</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.03452281384049945</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-0.01866942981561715</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.02800919204739094</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-0.2890971115849275</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-1.877446278800023</v>
+      <c r="AS4" t="n">
+        <v>-0.4617078840228436</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-0.4414127181628802</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-1.050605660461935</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>AHSZqech</t>
+          <t>QD438VuA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.548609129611189</v>
+        <v>1.705753661838491</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6628033029361787</v>
+        <v>0.2121025403664351</v>
       </c>
       <c r="D5" t="n">
-        <v>1.64964691859188</v>
+        <v>1.640946316499811</v>
       </c>
       <c r="E5" t="n">
-        <v>1.744065815566682</v>
+        <v>-0.2516569535949728</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.679560351381822</v>
+        <v>-0.2516569535947502</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1731686280403403</v>
+        <v>1.176596214785558</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.749474738089571</v>
+        <v>0.3035180056792265</v>
       </c>
       <c r="I5" t="n">
-        <v>1.231888417421724</v>
+        <v>-0.9732561483740877</v>
       </c>
       <c r="J5" t="n">
+        <v>1.42917190161448</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.3098378345505145</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.1082910774989508</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-0.5794543984791194</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.153797345706573</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.816671966961523</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.927046777817475</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-1.395670056776309</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.2514890836683851</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-1.311903499669944</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.2658165703092287</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.143160655252188</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.12933007244709</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.279456010852586</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-1.126045221306972</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.1949324761721781</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-0.09097050046553559</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.5522881472600919</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.2630959778203125</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.6346785727101361</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-1.561332632183451</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-0.4943145627197029</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.7258270831864968</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.7293033364295933</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.6561126563490299</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.8570232115091124</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.01303294829223868</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.356335977751574</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.7263252477042366</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-1.964544808367533</v>
+      </c>
+      <c r="AN5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
+      <c r="AO5" t="n">
+        <v>-0.8509860722786372</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-1.204268946049773</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-1.758616805964528</v>
+      </c>
+      <c r="AR5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
-        <v>0.005301117250606866</v>
-      </c>
-      <c r="M5" t="n">
-        <v>-0.645416299882146</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-0.2600142302074548</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-1.986318178756729</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-0.4679464381629391</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.409571531231081</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.5011472361027791</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-2.032453945476422</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.9732430994106843</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-1.449614501096117</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.9282631638113618</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.8835054702117573</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.05290597506377909</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.4069652406481492</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-0.4652468151276155</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-0.5915294114364474</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.1503433927337082</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-1.094698020140513</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-0.9504341191830969</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-2.513991759300129</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-0.01866942981561715</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-0.6821133619066498</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-1.926270991383776</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-1.141037837584753</v>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0.3472658352988922</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>xUcLQXdU</t>
+          <t>2uJ8nlJj</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.568324270223589</v>
+        <v>1.490019075068509</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02180865801600549</v>
+        <v>-1.354527266674561</v>
       </c>
       <c r="D6" t="n">
-        <v>1.665754057756553</v>
+        <v>1.657810658347641</v>
       </c>
       <c r="E6" t="n">
-        <v>1.607989243553732</v>
+        <v>-0.2516569535949728</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.679560351381822</v>
+        <v>-0.2516569535947502</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1731686280403403</v>
+        <v>-2.405502369875422</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.025394296898854</v>
+        <v>2.054494276931769</v>
       </c>
       <c r="I6" t="n">
-        <v>1.815905178912753</v>
+        <v>-3.356373902214216</v>
       </c>
       <c r="J6" t="n">
+        <v>3.251828599266162</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-1.683604293760059</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.943363614227337</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.393091262644291</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-1.412547937194114</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.273157478624273</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.683109866770759</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-4.781077972794521</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.1342423533565548</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.03046779856501466</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.550552019449979</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.8424413719273233</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-3.344414131919935</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.105422995109079</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.007755290070254</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0.05904057027215107</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0.129533155810735</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.6497636336379178</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.6495524461425821</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.1131332939824047</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-2.166313809978758</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-1.287256430858177</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.4804821784038139</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.100792457305637</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-4.927169769592366</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.115755955432503</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.3863933479199161</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>3.279739679987971</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.891842940695564</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-0.01563378957387318</v>
+      </c>
+      <c r="AN6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
+      <c r="AO6" t="n">
+        <v>0.3619649901176635</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.2874531381146473</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0.3082179989835359</v>
+      </c>
+      <c r="AR6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
-        <v>0.005301117250606866</v>
-      </c>
-      <c r="M6" t="n">
-        <v>-0.488509244201154</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.17412400602696</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-0.9654568758120402</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.9167478250955421</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.03704444156406628</v>
-      </c>
-      <c r="R6" t="n">
-        <v>-0.2296278241130858</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.3697867832185063</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-0.8070250860923833</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.7541494109650223</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.071192807447805</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.2873081681259866</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.4162497555470699</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-0.4373110078419221</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-0.9402111882861998</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-0.1102853820575653</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-1.839996995562729</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.619527232455776</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-0.5616347284583976</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.3799603696226323</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.08900920319669858</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>-0.09686708665209423</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.059922770253249</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0.3317790448457865</v>
+      <c r="AS6" t="n">
+        <v>-1.140962683219638</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-1.343998565834971</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.4920680922243942</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>EkZQoHSu</t>
+          <t>jeCjBXei</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.548609129611189</v>
+        <v>1.490019075068509</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.451354473291761</v>
+        <v>1.184493455081536</v>
       </c>
       <c r="D7" t="n">
-        <v>1.633539779427207</v>
+        <v>1.640946316499811</v>
       </c>
       <c r="E7" t="n">
-        <v>1.607989243553732</v>
+        <v>-0.2516569535949728</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.679560351381822</v>
+        <v>-0.2516569535947502</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1731686280403403</v>
+        <v>-1.058398857234461</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.648269067112023</v>
+        <v>1.30098773339452</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7711065692545437</v>
+        <v>1.920529695574641</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.4349955210771985</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.9127244604947443</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5119969453615547</v>
+        <v>0.7126037101825359</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9236542569277709</v>
+        <v>1.169228762029711</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3465570548078079</v>
+        <v>-1.016020769995652</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2857206966994373</v>
+        <v>1.003394053847506</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.221383022582995</v>
+        <v>0.1512166470166958</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.8064878322937878</v>
+        <v>-0.02297134651322572</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2499433091535757</v>
+        <v>1.221340740425477</v>
       </c>
       <c r="S7" t="n">
-        <v>1.857577297633989</v>
+        <v>0.631183850804242</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.05309563864441008</v>
+        <v>-0.3489772686733373</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3934862242063647</v>
+        <v>-0.5578838655974278</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6200053723574177</v>
+        <v>0.8072204897326646</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-1.79914820319434</v>
       </c>
       <c r="X7" t="n">
-        <v>0.9604704030556541</v>
+        <v>-0.6857308786127537</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.237733069162379</v>
+        <v>-0.05511827515932696</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.2002290007146056</v>
+        <v>0.01866170043437298</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.6794784658217567</v>
+        <v>1.453826982933599</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2896949791946303</v>
+        <v>-0.8715282604622421</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.9513956671344118</v>
+        <v>-0.1896173800107662</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.1205311896231058</v>
+        <v>0.2536109012024701</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.1507286831367867</v>
+        <v>-0.3810371529856356</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.01866942981561715</v>
+        <v>-1.698010126012166</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.1609351780866296</v>
+        <v>-1.096888825891096</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.8734766578352899</v>
+        <v>1.069634712478467</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>0.5166584380416065</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.8130162675581967</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-0.5670677244848222</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.5089044756761226</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.3589592842581647</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-0.3876869760723114</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-0.869464013652576</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-3.016830252704842</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-2.186245296813835</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.1906270819609855</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.02543444671425096</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.009880205673165195</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-0.4554912524926485</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>htYUpyrn</t>
+          <t>CA0a9BQ3</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.568324270223589</v>
+        <v>1.490019075068509</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.338899272428573</v>
+        <v>-1.138440396737872</v>
       </c>
       <c r="D8" t="n">
-        <v>1.633539779427207</v>
+        <v>1.674675000195472</v>
       </c>
       <c r="E8" t="n">
-        <v>1.659017958058589</v>
+        <v>-0.2516569535949728</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.679560351381822</v>
+        <v>-0.2516569535947502</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1731686280403403</v>
+        <v>-2.386812532376889</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0003863281213269582</v>
+        <v>1.096661754568412</v>
       </c>
       <c r="I8" t="n">
-        <v>1.733777821828077</v>
+        <v>-1.18603451925267</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.76056402846024</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-2.014179052544769</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5119969453615547</v>
+        <v>0.5512100940853352</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4529330898847959</v>
+        <v>0.8799810563733347</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.181077149168351</v>
+        <v>-3.607243974554175</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5284864943509182</v>
+        <v>3.239670416264751</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4272201363023957</v>
+        <v>1.499605561875161</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8805767154219183</v>
+        <v>-0.5218051057201359</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.2296278241130858</v>
+        <v>0.9434933105307529</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4069987738523333</v>
+        <v>-2.097938625410034</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1955767428226758</v>
+        <v>1.04187375036358</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5448072169094453</v>
+        <v>-1.134758704535273</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7144971406819669</v>
+        <v>-0.6601676092997197</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.354543918512267</v>
       </c>
       <c r="X8" t="n">
-        <v>0.9041717153823519</v>
+        <v>1.226582317121955</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36606305893287</v>
+        <v>-0.1302237949042986</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.1290036700902756</v>
+        <v>-0.4020909792686193</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.118687136188287</v>
+        <v>-0.1989942158011641</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.4917825388431389</v>
+        <v>-0.7194201898017598</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.001955124795360566</v>
+        <v>-1.036810442529471</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.1772169896452757</v>
+        <v>-2.166313809978758</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.217723663403094</v>
+        <v>-0.9474242016559736</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.01866942981561715</v>
+        <v>-0.8804188804597753</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.0462819524145119</v>
+        <v>1.484551679188034</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.6568075898050402</v>
+        <v>0.1736569743495645</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>2.056982794431339</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-0.006756964557535882</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.3946341266333761</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>2.35424043994835</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-2.48747338289632</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.23103613047979</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1.495842608559293</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-0.3682191908655664</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-0.2520296697656186</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.02880980714923306</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-1.346797470855029</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>-1.343998565834971</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-0.09773387296995954</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>lfn5UFc5</t>
+          <t>UoBfAiBc</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.588039410835988</v>
+        <v>1.490019075068509</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.181461991220109</v>
+        <v>1.427591183760311</v>
       </c>
       <c r="D9" t="n">
-        <v>1.60132550109786</v>
+        <v>1.674675000195472</v>
       </c>
       <c r="E9" t="n">
-        <v>1.744065815566682</v>
+        <v>-0.2516569535949728</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.679560351381822</v>
+        <v>-0.2516569535947502</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1731686280403403</v>
+        <v>-0.1941465003003828</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1512364200360595</v>
+        <v>-0.780566740409104</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8258581406443275</v>
+        <v>0.0480800318431105</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.4349955210771985</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.7951723223343644</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.501394710860341</v>
+        <v>-1.154955638804428</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.429951578287104</v>
+        <v>-0.32261793126906</v>
       </c>
       <c r="N9" t="n">
-        <v>2.398086811089091</v>
+        <v>-0.1163681237535856</v>
       </c>
       <c r="O9" t="n">
-        <v>2.414589999181653</v>
+        <v>-0.01056369895231336</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9778372778863575</v>
+        <v>1.909900469393746</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2060072305644681</v>
+        <v>0.572337827988241</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.1611176622178484</v>
+        <v>-0.5225745193528432</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.398759012383375</v>
+        <v>-0.5699257267484081</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7592686855606355</v>
+        <v>-1.123396843509429</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1642677224812781</v>
+        <v>1.03971573854622</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3729455677768237</v>
+        <v>1.582669485156282</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.1151250107819069</v>
+        <v>1.266941359575973</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.05290597506377909</v>
+        <v>-0.8784555889795443</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.325537799005347</v>
+        <v>0.4005026656076167</v>
       </c>
       <c r="Z9" t="n">
-        <v>-1.21510060715587</v>
+        <v>-1.741035917404611</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.2804869758257318</v>
+        <v>0.8528010924845945</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.5289799742729467</v>
+        <v>0.3453363048216173</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.6911276005994508</v>
+        <v>0.9127149059691704</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.195437260293279</v>
+        <v>0.5561014901001236</v>
       </c>
       <c r="AE9" t="n">
-        <v>-1.062642286431777</v>
+        <v>-0.52263391515322</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.01866942981561715</v>
+        <v>1.911950274954146</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.2638622882244098</v>
+        <v>0.7010483402743054</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.3343732745233834</v>
+        <v>1.046799592782852</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.035836631696857</v>
+        <v>-1.017051764863917</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.07174746210057568</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.3946341266333761</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>-0.3219534745741701</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>2.047141605399588</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-1.109530600383096</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.7297237364532005</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.38002618535866</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0.5342858823810098</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.1097184445551093</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-0.4205409264957652</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>-0.4414127181628802</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.4366429732914636</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>8lOY3V6E</t>
+          <t>I7sxhAeT</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.548609129611189</v>
+        <v>1.490019075068509</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6178212225909034</v>
+        <v>1.049439161371105</v>
       </c>
       <c r="D10" t="n">
-        <v>1.60132550109786</v>
+        <v>1.640946316499811</v>
       </c>
       <c r="E10" t="n">
-        <v>1.607989243553732</v>
+        <v>-0.2516569535949728</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.679560351381822</v>
+        <v>-0.2516569535947502</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1731686280403403</v>
+        <v>0.9275186506963532</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.372349508302739</v>
+        <v>0.2133967500032971</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.961953246982347</v>
+        <v>-0.803033451671221</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1.139203790624439</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.9270383110056515</v>
       </c>
       <c r="L10" t="n">
-        <v>0.005301117250606866</v>
+        <v>-0.4291259675631439</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.01778807715817907</v>
+        <v>0.04694766408297107</v>
       </c>
       <c r="N10" t="n">
-        <v>2.305362356160142</v>
+        <v>-0.7118391858268244</v>
       </c>
       <c r="O10" t="n">
-        <v>2.24652137003832</v>
+        <v>0.5321879751542336</v>
       </c>
       <c r="P10" t="n">
-        <v>1.161105636258803</v>
+        <v>0.4779996063945601</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.378374119655044</v>
+        <v>-1.077751965687159</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.2981379860083233</v>
+        <v>-0.4801288031997692</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.300273574208949</v>
+        <v>-2.504458442400608</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.834494153154156</v>
+        <v>1.581920155419731</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6202010764837922</v>
+        <v>-0.1352643452547167</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2828203368829457</v>
+        <v>-0.8033274238394645</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.6787527495751372</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1934007835069169</v>
+        <v>0.1310456918139478</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4609989205515137</v>
+        <v>-0.004582398581615172</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.7132732600060224</v>
+        <v>0.03296432885695855</v>
       </c>
       <c r="AA10" t="n">
-        <v>-2.019915908481591</v>
+        <v>-1.100533051474671</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.1725508168709069</v>
+        <v>-0.7194201898017598</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.368243403139605</v>
+        <v>-0.7645892482667036</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.1481342415439162</v>
+        <v>-1.258842043285798</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.4466975023736229</v>
+        <v>-0.3527178005521185</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.5117809333690518</v>
+        <v>0.6171647240046184</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.08844525724999652</v>
+        <v>1.872554627994959</v>
       </c>
       <c r="AH10" t="n">
-        <v>-1.013787647506801</v>
+        <v>-0.9938736679446682</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>-1.125085715419845</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-0.2577579910616892</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-1.047918650043921</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.03204042946320033</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-0.9091159371763048</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2.499687521170828</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-0.2870618567796285</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-0.4323435736101577</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0.9044302570083725</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.8378961812079954</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.04601792547779016</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.009880205673165195</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-0.4214191133374336</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>dKkDSgSH</t>
+          <t>OlK4mU3p</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.548609129611189</v>
+        <v>1.490019075068509</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.586300714327587</v>
+        <v>-0.8323173309942289</v>
       </c>
       <c r="D11" t="n">
-        <v>1.665754057756553</v>
+        <v>1.674675000195472</v>
       </c>
       <c r="E11" t="n">
-        <v>1.64200838655697</v>
+        <v>-0.2516569535949728</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.679560351381822</v>
+        <v>-0.2516569535947502</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1731686280403403</v>
+        <v>0.3117402208862462</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4672489568143441</v>
+        <v>-0.7920859986533954</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4334280013207057</v>
+        <v>-1.824369631888419</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-1.346237160718763</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.0706374268945627</v>
       </c>
       <c r="L11" t="n">
-        <v>0.005301117250606866</v>
+        <v>-1.91160442510114</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.01778807715817907</v>
+        <v>0.0537982676379901</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5435977125101054</v>
+        <v>0.4317480540653731</v>
       </c>
       <c r="O11" t="n">
-        <v>2.62000721257906</v>
+        <v>-0.5851966051725004</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9770252114197339</v>
+        <v>2.704345853894716</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2346015449325314</v>
+        <v>1.580422879508985</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3869636329440505</v>
+        <v>1.030808815432247</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1115572067394411</v>
+        <v>0.1363232330106567</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.091702590821322</v>
+        <v>0.3513306467105737</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6241654093246697</v>
+        <v>0.6242105092856008</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1984503590837808</v>
+        <v>0.6282707215579836</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5108821564081507</v>
+        <v>-0.9356372651080072</v>
       </c>
       <c r="X11" t="n">
-        <v>1.58913908207419</v>
+        <v>-0.6663248334993191</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.6298541702495279</v>
+        <v>0.7926991191983066</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.706501837534286</v>
+        <v>1.513178832035002</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.003652029061147204</v>
+        <v>0.2517752020355895</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.685431586217571</v>
+        <v>0.6495524461425821</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.8829808688032169</v>
+        <v>-0.4949358069430779</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.7971010582237827</v>
+        <v>0.25361090120247</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.8870266798774514</v>
+        <v>-0.6075919724537707</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.1737477748108026</v>
+        <v>-0.7625516664181186</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.8415152967205748</v>
+        <v>0.5859060038580857</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0.217424421219027</v>
+        <v>-0.2073305979989806</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.7525838683973691</v>
+        <v>0.7778581817966959</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.05115996220084684</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.3946341266333761</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.0910460757097257</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.3585227990633125</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-0.8001690471070457</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-2.524519342372521</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-0.3650375958315095</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-1.005276289060581</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.1906270819609855</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.03229560630209736</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.009880205673165195</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-0.967531360256716</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>ITj9TZCB</t>
+          <t>6XwYhjtN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.666899973285585</v>
+        <v>1.509631310229416</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.5067307860409794</v>
+        <v>1.166486215920145</v>
       </c>
       <c r="D12" t="n">
-        <v>1.665754057756553</v>
+        <v>1.640946316499811</v>
       </c>
       <c r="E12" t="n">
-        <v>1.624998815055351</v>
+        <v>-0.2516569535949728</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.679560351381822</v>
+        <v>-0.2516569535947502</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1731686280403403</v>
+        <v>-1.562114432562264</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1655487729848791</v>
+        <v>-1.163349240960911</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8669218191866657</v>
+        <v>-1.271145867604104</v>
       </c>
       <c r="J12" t="n">
+        <v>1.222051822335879</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-1.122993159888277</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-1.651617531428432</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-2.239013109682579</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.6710195202104043</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-1.314562367790741</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.2961396053062705</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-3.411998328022319</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.1672286519834572</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.4808186709255138</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.8621541189973584</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.7987016369933219</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-1.089647052918954</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-1.035754475320916</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-1.002358146497622</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.04248786517039847</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0.5598923894631641</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.6497636336379178</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-1.175744401783207</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.3751779950017041</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.351370276592837</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0.2394403908180506</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.8137809169765151</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.063577640752383</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-0.7705640708261856</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.390238295041555</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.001519401438498179</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-0.08621679892572301</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.3768990069447677</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-0.1173884758667102</v>
+      </c>
+      <c r="AN12" t="n">
         <v>0</v>
       </c>
-      <c r="K12" t="n">
+      <c r="AO12" t="n">
+        <v>0.1733251613963935</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0.795858836151772</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.3224359020177915</v>
+      </c>
+      <c r="AR12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="n">
-        <v>0.005301117250606866</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.865096591013721</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.450873257581156</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.3790921573346222</v>
-      </c>
-      <c r="P12" t="n">
-        <v>-0.9770252114197339</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.230857066430688</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.414616061372611</v>
-      </c>
-      <c r="S12" t="n">
-        <v>-3.007545922270248</v>
-      </c>
-      <c r="T12" t="n">
-        <v>-0.05931244818109239</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.3698435035256368</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.3882894653116527</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0.8338223617046083</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.3224186094249008</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>-0.01179577860292617</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>-0.8056087486918393</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.129996570615469</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>-0.0906071591548982</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.85084290970916</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>-1.212323088460119</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>-0.0600427232437486</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>-0.6040441964223112</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>-0.2810733936930713</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0.286202481308027</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0.5772485252508767</v>
+      <c r="AS12" t="n">
+        <v>-0.928266735996399</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-0.8927056419989258</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-0.3956906454490525</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>jDDw3kMK</t>
+          <t>CAvUgWQG</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.548609129611189</v>
+        <v>1.490019075068509</v>
       </c>
       <c r="C13" t="n">
-        <v>1.472480749151134</v>
+        <v>-1.45356708206221</v>
       </c>
       <c r="D13" t="n">
-        <v>1.665754057756553</v>
+        <v>1.674675000195472</v>
       </c>
       <c r="E13" t="n">
-        <v>1.624998815055351</v>
+        <v>-0.2516569535949728</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.679560351381822</v>
+        <v>-0.2516569535947502</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1731686280403403</v>
+        <v>-0.1636238892357164</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.598624646174838</v>
+        <v>0.7572689406399091</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.688195390033427</v>
+        <v>0.7289708186545762</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.973421018017283</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1.35877826066797</v>
       </c>
       <c r="L13" t="n">
-        <v>0.005301117250606866</v>
+        <v>0.1937362500442377</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.01778807715817907</v>
+        <v>0.3056435808293923</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6363221674390546</v>
+        <v>-1.268138078865874</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.08776514584130231</v>
+        <v>1.415536663422803</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3661306835115803</v>
+        <v>0.4341135593938649</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.19511417347061</v>
+        <v>1.171874407228749</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.2981379860083233</v>
+        <v>-0.9321486887546043</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7937770350262913</v>
+        <v>0.401349785720398</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.063892352857831</v>
+        <v>2.935398254980182</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.73988488643127</v>
+        <v>0.9539719724454384</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3789310272846069</v>
+        <v>2.024078913320495</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.9050864360455548</v>
+        <v>-1.498796572555616</v>
       </c>
       <c r="X13" t="n">
-        <v>0.5596028954559409</v>
+        <v>-0.4643696503756505</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.06925474125212067</v>
+        <v>1.096370380352168</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.2332864449747709</v>
+        <v>0.7270376836747721</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.6417868294259708</v>
+        <v>-0.6497636336379178</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.1059285444593107</v>
+        <v>-0.2630959778203125</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.2039317493932008</v>
+        <v>-1.67792951686795</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.2298094530120961</v>
+        <v>-0.8353552188290827</v>
       </c>
       <c r="AE13" t="n">
-        <v>-1.005878550262166</v>
+        <v>0.157030543251186</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.4754606813241728</v>
+        <v>0.4867631053318883</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.2811594235812983</v>
+        <v>-0.3499125513616542</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.07421933104221948</v>
+        <v>0.203950590819667</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.8577850742852648</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>vquIRDsO</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.765475676347582</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1.011414425612062</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.617432640262533</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.77808495856992</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-0.679560351381822</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-0.1731686280403403</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.3171715211422649</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-1.920889568440009</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-0.501394710860341</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-0.959230411244129</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.8217710772969532</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.2857206966994373</v>
-      </c>
-      <c r="P14" t="n">
-        <v>-0.7937568530472879</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-0.2631958593005946</v>
-      </c>
-      <c r="R14" t="n">
-        <v>-0.02409733842737382</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-1.946889337383207</v>
-      </c>
-      <c r="T14" t="n">
-        <v>-1.50579447801491</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.1943490399542722</v>
-      </c>
-      <c r="V14" t="n">
-        <v>-0.526437370464033</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0.138258842604544</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-0.2421321197434866</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>-0.03205840856668788</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0.1416423254102747</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>-0.06147058213054238</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>-0.6491238762054466</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>-0.319225669550273</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0.6622259278232673</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0.3724844804961435</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.670767013209108</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.612370886214873</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0.8037657402951246</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0.8577850742852648</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>A3m1Vera</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.726045395122783</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.9453060694074138</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1.746289753579919</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.795094530071538</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-0.679560351381822</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-0.1731686280403403</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.041251962332981</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.3649885370834756</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.005301117250606866</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-0.01778807715817907</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-1.032718021282032</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-2.14193727981537</v>
-      </c>
-      <c r="P15" t="n">
-        <v>-2.504261531190118</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.659771781951631</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.757166870848798</v>
-      </c>
-      <c r="S15" t="n">
-        <v>-0.9014506190362108</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.9308557616606022</v>
-      </c>
-      <c r="U15" t="n">
-        <v>-0.4649110003883377</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-1.327742320589182</v>
-      </c>
-      <c r="W15" t="n">
-        <v>-0.5324631222419481</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-0.287483840369203</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>-0.4845904777573661</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.775668639525224</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>-1.23834430952069</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>-0.2244068895815206</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0.1456574304872854</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>-0.0685028213227811</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0.9656897103681585</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>-0.01866942981561715</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0.9362909846040977</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>-0.2768603107907496</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0.787650937026668</v>
+        <v>-1.078455759218183</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.5683883563241952</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.3946341266333761</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.05076784890259671</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-0.3957032729903753</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-0.2020700441066813</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-0.3259533689496013</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-2.961215480176765</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-1.620023935099486</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-2.544084862357632</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-1.676133131071657</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-1.343998565834971</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-2.206439230869294</v>
       </c>
     </row>
   </sheetData>

--- a/data/usa/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/usa/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU13"/>
+  <dimension ref="A1:AG14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,1968 +436,1497 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>id_team_away</t>
+          <t>id_coach_away</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_away</t>
+          <t>dif_mean_last_60_matches_expected_points</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>id_competition</t>
+          <t>dif_mean_last_360_matches_expected_points</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>is_cup</t>
+          <t>dif_mean_last_60_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_shots_on_goal</t>
+          <t>dif_mean_last_60_matches_goal_attempts</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_shots_on_goal_against</t>
+          <t>dif_mean_last_360_matches_goal_attempts</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goal_attempts</t>
+          <t>dif_mean_last_60_matches_points</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goal_attempts_against</t>
+          <t>dif_mean_last_360_matches_attacks</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_goal_attempts</t>
+          <t>dif_mean_last_60_matches_dangerous_attacks</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_goal_attempts_against</t>
+          <t>dif_mean_last_360_matches_dead_balls</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_goals_against</t>
+          <t>dif_mean_last_60_matches_yellow_cards</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_points</t>
+          <t>dif_mean_last_360_matches_yellow_cards</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_points_against</t>
+          <t>dif_mean_last_360_matches_red_cards</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goal_ratio</t>
+          <t>dif_mean_last_60_matches_defensive_actions</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goal_ratio_against</t>
+          <t>dif_mean_last_60_matches_PPDA</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_goal_ratio</t>
+          <t>dif_mean_last_360_matches_KGP</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_PPS_against</t>
+          <t>dif_mean_last_60_matches_clean_sheet</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_PPS</t>
+          <t>dif_mean_last_360_matches_clean_sheet</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_attacks</t>
+          <t>dif_mean_age_player_sub</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_dangerous_attacks</t>
+          <t>dif_mean_rep_player_sub</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_dangerous_attacks_against</t>
+          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_dangerous_attacks_against</t>
+          <t>dif_sum_value_player_miss</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_dead_balls</t>
+          <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_dead_balls_against</t>
+          <t>dif_mean_rep_player_start</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_yellow_cards</t>
+          <t>dif_mean_pot_player_start</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_yellow_cards_against</t>
+          <t>dif_mean_hei_player_start</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_yellow_cards</t>
+          <t>dif_mean_age_player_miss</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_red_cards_against</t>
+          <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_defensive_actions</t>
+          <t>dif_sum_wage_player_miss</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_360_matches_defensive_actions_against</t>
+          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_PPDA</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_PPDA_against</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_PPDA</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_KGP</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_60_matches_clean_sheet_against</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_clean_sheet_against</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>mean_last_360_matches_mean_rat_player_start_away_against</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_360_matches_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
+          <t>dif_mean_value_player_sub</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Kz477keG</t>
+          <t>f92nPEMI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.627304721194861</v>
+        <v>1.639703782661902</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.273494690448302</v>
+        <v>1.65010083665649</v>
       </c>
       <c r="D2" t="n">
-        <v>1.691539342043302</v>
+        <v>-0.3926738151284457</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2516569535949728</v>
+        <v>1.564618624730012</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2516569535947502</v>
+        <v>1.264961318226301</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.736925750478082</v>
+        <v>0.3820548574099833</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.459252962573645</v>
+        <v>1.751139188157838</v>
       </c>
       <c r="I2" t="n">
-        <v>-4.760711150012864</v>
+        <v>0.05388791527955013</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.7248769228829627</v>
+        <v>0.7770343103435792</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.258165895212692</v>
+        <v>-0.7683740290520267</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8874034089071657</v>
+        <v>1.202747679294955</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5794543984791194</v>
+        <v>0.9560246312678727</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6566194999040601</v>
+        <v>-0.8084479668795894</v>
       </c>
       <c r="O2" t="n">
-        <v>1.423834836769957</v>
+        <v>0.4908246634495644</v>
       </c>
       <c r="P2" t="n">
-        <v>2.857142785188833</v>
+        <v>0.5462970652149391</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.8575818249925836</v>
+        <v>1.556603681801954</v>
       </c>
       <c r="R2" t="n">
-        <v>2.160502142878789</v>
+        <v>0.919438852822512</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2246774835314991</v>
+        <v>-0.5915128176616505</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.547274165227749</v>
+        <v>-0.04089450827897085</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4630832862497295</v>
+        <v>0.7767215246693251</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.304386774728571</v>
+        <v>-0.1134675802983055</v>
       </c>
       <c r="W2" t="n">
-        <v>1.579807641491311</v>
+        <v>1.030312901378972</v>
       </c>
       <c r="X2" t="n">
-        <v>1.049037240584286</v>
+        <v>-0.2008493473938932</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.6302031019669018</v>
+        <v>-0.8575202256861933</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1.360967283167446</v>
+        <v>-0.5041750260662521</v>
       </c>
       <c r="AA2" t="n">
-        <v>-2.002071887148178</v>
+        <v>1.03933202460872</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1.632068613764654</v>
+        <v>-1.334275812388559</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.5101769171800056</v>
+        <v>0.2304755486362986</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.351370276592837</v>
+        <v>-0.3382291311577872</v>
       </c>
       <c r="AE2" t="n">
-        <v>-2.731543404967539</v>
+        <v>-0.9591836376682054</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.7693880912438136</v>
+        <v>0.864576070259466</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.153466340643142</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-0.8892904958489537</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1.931173419576069</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-0.5756621832978706</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.3946341266333761</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.075751488463705</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-0.006536957239599399</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0.3341566482384736</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-0.1430987407700007</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0.7843594032959015</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-0.6204838874312193</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0.7569875438021191</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0.5949106925055023</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0.4611731295092106</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0.4602988085585026</v>
+        <v>-0.6544632203899884</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zJAPgoq7</t>
+          <t>SvGeZbpQ</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.509631310229416</v>
+        <v>1.462522983494052</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.6342377002189306</v>
+        <v>1.70061479785879</v>
       </c>
       <c r="D3" t="n">
-        <v>1.657810658347641</v>
+        <v>-0.3926738151284457</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2516569535949728</v>
+        <v>1.105344127307445</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2516569535947502</v>
+        <v>0.5801932119528321</v>
       </c>
       <c r="G3" t="n">
-        <v>1.594772308623398</v>
+        <v>0.3442378606926271</v>
       </c>
       <c r="H3" t="n">
-        <v>1.615453391497765</v>
+        <v>1.139928744626126</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6013037961274265</v>
+        <v>-0.1995272888524871</v>
       </c>
       <c r="J3" t="n">
-        <v>2.381924266296041</v>
+        <v>1.075122791241085</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8733226096479751</v>
+        <v>1.514240202050277</v>
       </c>
       <c r="L3" t="n">
-        <v>1.633848883356718</v>
+        <v>0.172647298789338</v>
       </c>
       <c r="M3" t="n">
-        <v>2.165687108015928</v>
+        <v>2.072163172986131</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.257460055948077</v>
+        <v>1.491874829663495</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2978866100581311</v>
+        <v>-0.2684856027135448</v>
       </c>
       <c r="P3" t="n">
-        <v>1.899395610297512</v>
+        <v>-1.256373886002814</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.435528444315844</v>
+        <v>-0.3174440644911753</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.9627021891301512</v>
+        <v>0.02078973956978617</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4105222223739407</v>
+        <v>0.1220534089935055</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1121369715426597</v>
+        <v>0.8681342996451273</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6914730880947857</v>
+        <v>-1.855128511696165</v>
       </c>
       <c r="V3" t="n">
-        <v>1.988288959685559</v>
+        <v>-0.05177443596850895</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4159450727662533</v>
+        <v>-0.1776900009254862</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3764794645056244</v>
+        <v>0.1719174260125117</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.1897599197159128</v>
+        <v>-0.06530597282973094</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.8885335880839144</v>
+        <v>-1.012011523948888</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.153314037709097</v>
+        <v>0.03596021881691078</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1.632068613764654</v>
+        <v>-0.744996939446509</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.3855041425575755</v>
+        <v>-1.662996819477599</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1.077347689947205</v>
+        <v>1.088310851475247</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.09784362865046625</v>
+        <v>-0.3467875687359928</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.5822131351521155</v>
+        <v>-1.100026431927365</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.7698531147526216</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.777390314706113</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-0.2626058983090887</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.642779755129289</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0.3946341266333761</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>-0.589161776331411</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>-0.7370667898635007</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.262241308066626</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0.3735028596140627</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0.3268929031676678</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0.9023475351224602</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.080622093425624</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0.5262990966270383</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0.4611731295092106</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0.2085126830997785</v>
+        <v>0.2099450179496589</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tdBLfRT0</t>
+          <t>CpDsQf7C</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.490019075068509</v>
+        <v>1.482209738957147</v>
       </c>
       <c r="C4" t="n">
-        <v>1.490616520825179</v>
+        <v>1.683776810791356</v>
       </c>
       <c r="D4" t="n">
-        <v>1.657810658347641</v>
+        <v>-0.3926738151284457</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2516569535949728</v>
+        <v>0.5197206964167282</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2516569535947502</v>
+        <v>-0.3725276315580808</v>
       </c>
       <c r="G4" t="n">
-        <v>1.21087294378866</v>
+        <v>-0.9793570244148383</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2379404111235494</v>
+        <v>-0.3276067600975719</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03703131650832238</v>
+        <v>-0.4529424929845243</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02075536251999814</v>
+        <v>-1.367597081862256</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8266747637320989</v>
+        <v>-1.876864007095318</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1787032156416357</v>
+        <v>-0.1376118126509934</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2133752710077678</v>
+        <v>-1.332059379254559</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7775146287757358</v>
+        <v>0.2474001967336861</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9191788141910679</v>
+        <v>0.3642729524223796</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7685471099258061</v>
+        <v>-0.310291259122575</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.776478482253063</v>
+        <v>0.06067336058587367</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.707828456193103</v>
+        <v>1.067192713290451</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.375852880156183</v>
+        <v>-0.5915128176616505</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8597176047403037</v>
+        <v>-1.740534578267323</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6120862388681664</v>
+        <v>0.427495437520273</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1948982120455491</v>
+        <v>-0.01064567308197746</v>
       </c>
       <c r="W4" t="n">
-        <v>-2.399851464471789</v>
+        <v>-0.09998005545853857</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5937649043906937</v>
+        <v>0.2706562439683749</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.9083738159492073</v>
+        <v>1.695170144629074</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.2719881414388846</v>
+        <v>-0.05599840329303701</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1.551302469311425</v>
+        <v>0.2715372851586604</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.2630959778203125</v>
+        <v>-0.9064341053145115</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3.37231564190536</v>
+        <v>-0.02198743377888768</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.25361090120247</v>
+        <v>-0.2090348029698345</v>
       </c>
       <c r="AE4" t="n">
-        <v>-2.646585347666988</v>
+        <v>1.665370943469848</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.3026139300086442</v>
+        <v>0.6983345754854859</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.439112920508937</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.794168261626826</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.8145801409566152</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.011982950130581</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0.3946341266333761</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>-1.246905288349235</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>-1.335518019400521</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>-1.400553014080995</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>-0.1617939260657689</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>-1.217766578198519</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>-0.4617078840228436</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>-0.4414127181628802</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>-1.050605660461935</v>
+        <v>-0.5219586498579797</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QD438VuA</t>
+          <t>YgEwRzh6</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.705753661838491</v>
+        <v>1.482209738957147</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2121025403664351</v>
+        <v>1.633262849589056</v>
       </c>
       <c r="D5" t="n">
-        <v>1.640946316499811</v>
+        <v>-0.3926738151284457</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2516569535949728</v>
+        <v>2.209540788199337</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2516569535947502</v>
+        <v>2.366544793535794</v>
       </c>
       <c r="G5" t="n">
-        <v>1.176596214785558</v>
+        <v>0.9240984770254214</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3035180056792265</v>
+        <v>0.9492412173364204</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9732561483740877</v>
+        <v>0.4340107214776059</v>
       </c>
       <c r="J5" t="n">
-        <v>1.42917190161448</v>
+        <v>-0.03045507585555042</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3098378345505145</v>
+        <v>1.696557632649502</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1082910774989508</v>
+        <v>1.671746773506421</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5794543984791194</v>
+        <v>0.230534579151004</v>
       </c>
       <c r="N5" t="n">
-        <v>1.153797345706573</v>
+        <v>0.5303399007084855</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.816671966961523</v>
+        <v>0.5541005189631568</v>
       </c>
       <c r="P5" t="n">
-        <v>2.927046777817475</v>
+        <v>-0.4509251631182859</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.395670056776309</v>
+        <v>-1.147779305489272</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.2514890836683851</v>
+        <v>0.03693476752198733</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.311903499669944</v>
+        <v>-0.9482959309892286</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2658165703092287</v>
+        <v>-0.414258064637068</v>
       </c>
       <c r="U5" t="n">
-        <v>0.143160655252188</v>
+        <v>-1.705282794698891</v>
       </c>
       <c r="V5" t="n">
-        <v>1.12933007244709</v>
+        <v>-0.05862922978293198</v>
       </c>
       <c r="W5" t="n">
-        <v>1.279456010852586</v>
+        <v>-0.4148405563103717</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.126045221306972</v>
+        <v>-0.08435973070439166</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.1949324761721781</v>
+        <v>-0.4512565062726228</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.09097050046553559</v>
+        <v>-0.5661994693964725</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.5522881472600919</v>
+        <v>2.315283378033967</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.2630959778203125</v>
+        <v>-0.9960877207483989</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6346785727101361</v>
+        <v>0.01220026175650198</v>
       </c>
       <c r="AD5" t="n">
-        <v>-1.561332632183451</v>
+        <v>0.8757369385388822</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.4943145627197029</v>
+        <v>-0.6092430268497981</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.7258270831864968</v>
+        <v>1.367952453727915</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.7293033364295933</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-0.6561126563490299</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-0.8570232115091124</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0.01303294829223868</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.356335977751574</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0.7263252477042366</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-1.964544808367533</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>-0.8509860722786372</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-1.204268946049773</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-1.758616805964528</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>-0.3472658352988922</v>
+        <v>0.609481980825185</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2uJ8nlJj</t>
+          <t>4K9ZRGx0</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.490019075068509</v>
+        <v>1.501896494420241</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.354527266674561</v>
+        <v>1.767966746128523</v>
       </c>
       <c r="D6" t="n">
-        <v>1.657810658347641</v>
+        <v>-0.3926738151284457</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2516569535949728</v>
+        <v>0.2995789963863329</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2516569535947502</v>
+        <v>-1.503883633227289</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.405502369875422</v>
+        <v>-1.004568355559742</v>
       </c>
       <c r="H6" t="n">
-        <v>2.054494276931769</v>
+        <v>-0.06397232624659241</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.356373902214216</v>
+        <v>-0.9597729012485987</v>
       </c>
       <c r="J6" t="n">
-        <v>3.251828599266162</v>
+        <v>0.5574157753003801</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.683604293760059</v>
+        <v>-0.3162268011659476</v>
       </c>
       <c r="L6" t="n">
-        <v>1.943363614227337</v>
+        <v>0.5605036690797751</v>
       </c>
       <c r="M6" t="n">
-        <v>1.393091262644291</v>
+        <v>-0.6623762542236037</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.412547937194114</v>
+        <v>-0.2934632008035062</v>
       </c>
       <c r="O6" t="n">
-        <v>1.273157478624273</v>
+        <v>0.04789367485441742</v>
       </c>
       <c r="P6" t="n">
-        <v>1.683109866770759</v>
+        <v>-0.5404194656610116</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.781077972794521</v>
+        <v>0.6858889402711393</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.1342423533565548</v>
+        <v>1.439273863839726</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03046779856501466</v>
+        <v>-0.4131212609978615</v>
       </c>
       <c r="T6" t="n">
-        <v>1.550552019449979</v>
+        <v>-1.052759606028723</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8424413719273233</v>
+        <v>-0.3815489840372934</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.344414131919935</v>
+        <v>-0.01064567308197746</v>
       </c>
       <c r="W6" t="n">
-        <v>2.105422995109079</v>
+        <v>-0.9714063832654428</v>
       </c>
       <c r="X6" t="n">
-        <v>1.007755290070254</v>
+        <v>0.1264310042575635</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.05904057027215107</v>
+        <v>0.4018973044958751</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.129533155810735</v>
+        <v>-0.05599840329303701</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.6497636336379178</v>
+        <v>-0.791899452883096</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6495524461425821</v>
+        <v>-0.6933942382793528</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1131332939824047</v>
+        <v>-2.083768456836243</v>
       </c>
       <c r="AD6" t="n">
-        <v>-2.166313809978758</v>
+        <v>-0.8660583041243441</v>
       </c>
       <c r="AE6" t="n">
-        <v>-1.287256430858177</v>
+        <v>0.178123347491618</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.4804821784038139</v>
+        <v>-1.423084794633054</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.100792457305637</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>-4.927169769592366</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.115755955432503</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0.3863933479199161</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>3.279739679987971</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0.891842940695564</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>-0.01563378957387318</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0.3619649901176635</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>-0.2874531381146473</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>-0.3082179989835359</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>-1.140962683219638</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>-1.343998565834971</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0.4920680922243942</v>
+        <v>-0.8748665944735711</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>jeCjBXei</t>
+          <t>r5LQTx8m</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.490019075068509</v>
+        <v>1.482209738957147</v>
       </c>
       <c r="C7" t="n">
-        <v>1.184493455081536</v>
+        <v>1.801642720263389</v>
       </c>
       <c r="D7" t="n">
-        <v>1.640946316499811</v>
+        <v>-0.3926738151284457</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2516569535949728</v>
+        <v>-0.1511336519473441</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2516569535947502</v>
+        <v>1.925911403411996</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.058398857234461</v>
+        <v>1.350169973374301</v>
       </c>
       <c r="H7" t="n">
-        <v>1.30098773339452</v>
+        <v>0.1621895011744144</v>
       </c>
       <c r="I7" t="n">
-        <v>1.920529695574641</v>
+        <v>0.05388791527955013</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4349955210771985</v>
+        <v>1.162527871854451</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9127244604947443</v>
+        <v>2.23621722722321</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7126037101825359</v>
+        <v>1.675817429500068</v>
       </c>
       <c r="M7" t="n">
-        <v>1.169228762029711</v>
+        <v>0.3421484333228298</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.016020769995652</v>
+        <v>0.538405967657403</v>
       </c>
       <c r="O7" t="n">
-        <v>1.003394053847506</v>
+        <v>0.5224625912063606</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1512166470166958</v>
+        <v>0.9758697174200209</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.02297134651322572</v>
+        <v>-1.92693299393031</v>
       </c>
       <c r="R7" t="n">
-        <v>1.221340740425477</v>
+        <v>1.005406604971675</v>
       </c>
       <c r="S7" t="n">
-        <v>0.631183850804242</v>
+        <v>-0.4844778836633771</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3489772686733373</v>
+        <v>-1.111845062065968</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5578838655974278</v>
+        <v>0.1558699200400664</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8072204897326646</v>
+        <v>-0.2934236353083974</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.79914820319434</v>
+        <v>-0.9231469296509309</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6857308786127537</v>
+        <v>0.2124114356236241</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.05511827515932696</v>
+        <v>0.0836573909552449</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01866170043437298</v>
+        <v>-1.766086476551438</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.453826982933599</v>
+        <v>-1.958285796463688</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.8715282604622421</v>
+        <v>-0.2877488978609146</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.1896173800107662</v>
+        <v>0.721375792221383</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.2536109012024701</v>
+        <v>-1.364559061948562</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.3810371529856356</v>
+        <v>0.3530936529008216</v>
       </c>
       <c r="AF7" t="n">
-        <v>-1.698010126012166</v>
+        <v>-2.400905320358091</v>
       </c>
       <c r="AG7" t="n">
-        <v>-1.096888825891096</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.069634712478467</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0.5166584380416065</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0.8130162675581967</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>-0.5670677244848222</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0.5089044756761226</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.3589592842581647</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>-0.3876869760723114</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>-0.869464013652576</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>-3.016830252704842</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>-2.186245296813835</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0.1906270819609855</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0.02543444671425096</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0.009880205673165195</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>-0.4554912524926485</v>
+        <v>-1.29700636467882</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>CA0a9BQ3</t>
+          <t>QTAVSdNg</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.490019075068509</v>
+        <v>1.679077293588091</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.138440396737872</v>
+        <v>1.633262849589056</v>
       </c>
       <c r="D8" t="n">
-        <v>1.674675000195472</v>
+        <v>-0.3926738151284457</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2516569535949728</v>
+        <v>0.9358521531087279</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2516569535947502</v>
+        <v>-1.027523211471833</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.386812532376889</v>
+        <v>-1.609640303037441</v>
       </c>
       <c r="H8" t="n">
-        <v>1.096661754568412</v>
+        <v>0.1570570397116148</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.18603451925267</v>
+        <v>-0.7063576971165615</v>
       </c>
       <c r="J8" t="n">
-        <v>1.76056402846024</v>
+        <v>0.3052857350695174</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.014179052544769</v>
+        <v>-2.948890499018764</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5512100940853352</v>
+        <v>0.1337639061389985</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8799810563733347</v>
+        <v>0.6769899958383077</v>
       </c>
       <c r="N8" t="n">
-        <v>-3.607243974554175</v>
+        <v>1.120756085154544</v>
       </c>
       <c r="O8" t="n">
-        <v>3.239670416264751</v>
+        <v>0.8388418687743228</v>
       </c>
       <c r="P8" t="n">
-        <v>1.499605561875161</v>
+        <v>-2.25359611433604</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.5218051057201359</v>
+        <v>4.619515337358719</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9434933105307529</v>
+        <v>1.73597414278778</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.097938625410034</v>
+        <v>-1.305079044316806</v>
       </c>
       <c r="T8" t="n">
-        <v>1.04187375036358</v>
+        <v>-1.077396321452196</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.134758704535273</v>
+        <v>-0.5017813030055963</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6601676092997197</v>
+        <v>-0.07934940199470539</v>
       </c>
       <c r="W8" t="n">
-        <v>1.354543918512267</v>
+        <v>-0.5541696616484693</v>
       </c>
       <c r="X8" t="n">
-        <v>1.226582317121955</v>
+        <v>0.1708080010916593</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.1302237949042986</v>
+        <v>0.03625995702366168</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.4020909792686193</v>
+        <v>0.6769571152006576</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.1989942158011641</v>
+        <v>-0.139758834085916</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.7194201898017598</v>
+        <v>1.77394084890093</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1.036810442529471</v>
+        <v>-0.6110677260809895</v>
       </c>
       <c r="AD8" t="n">
-        <v>-2.166313809978758</v>
+        <v>-0.4575582456727306</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.9474242016559736</v>
+        <v>0.003153042082414373</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.8804188804597753</v>
+        <v>-0.1857446831894082</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.484551679188034</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.1736569743495645</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>2.056982794431339</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>-0.006756964557535882</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0.3946341266333761</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>2.35424043994835</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>-2.48747338289632</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0.23103613047979</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1.495842608559293</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>-0.3682191908655664</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>-0.2520296697656186</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0.02880980714923306</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>-1.346797470855029</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>-1.343998565834971</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>-0.09773387296995954</v>
+        <v>0.07616794290886465</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>UoBfAiBc</t>
+          <t>YuZ4CywD</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.490019075068509</v>
+        <v>1.462522983494052</v>
       </c>
       <c r="C9" t="n">
-        <v>1.427591183760311</v>
+        <v>1.751128759061089</v>
       </c>
       <c r="D9" t="n">
-        <v>1.674675000195472</v>
+        <v>-0.3926738151284457</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2516569535949728</v>
+        <v>0.2173318378872081</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2516569535947502</v>
+        <v>-0.312982578838649</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1941465003003828</v>
+        <v>-0.6011870572412765</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.780566740409104</v>
+        <v>-0.6912770355795217</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0480800318431105</v>
+        <v>-1.72001851364471</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4349955210771985</v>
+        <v>-0.6350110032032291</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7951723223343644</v>
+        <v>-0.1047385816708456</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.154955638804428</v>
+        <v>0.3487290037181169</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.32261793126906</v>
+        <v>1.011831558353785</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1163681237535856</v>
+        <v>0.1308101518352133</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.01056369895231336</v>
+        <v>-0.4266752414975257</v>
       </c>
       <c r="P9" t="n">
-        <v>1.909900469393746</v>
+        <v>-0.208012056216603</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.572337827988241</v>
+        <v>0.3135847629812497</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.5225745193528432</v>
+        <v>0.6246673196401288</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5699257267484081</v>
+        <v>-1.305079044316806</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.123396843509429</v>
+        <v>-0.4258920691425965</v>
       </c>
       <c r="U9" t="n">
-        <v>1.03971573854622</v>
+        <v>0.4346723092724359</v>
       </c>
       <c r="V9" t="n">
-        <v>1.582669485156282</v>
+        <v>-1.522127709162008</v>
       </c>
       <c r="W9" t="n">
-        <v>1.266941359575973</v>
+        <v>-0.2010570510886022</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8784555889795443</v>
+        <v>0.1669250138686759</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4005026656076167</v>
+        <v>0.5779449162417557</v>
       </c>
       <c r="Z9" t="n">
-        <v>-1.741035917404611</v>
+        <v>-0.05599840329303701</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.8528010924845945</v>
+        <v>-2.37131973383845</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3453363048216173</v>
+        <v>-0.7545578093520823</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.9127149059691704</v>
+        <v>1.45772615759901</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.5561014901001236</v>
+        <v>-1.408170600030434</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.52263391515322</v>
+        <v>0.6155491110146269</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.911950274954146</v>
+        <v>-0.5395817951931069</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.7010483402743054</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.046799592782852</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-1.017051764863917</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0.07174746210057568</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0.3946341266333761</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>-0.3219534745741701</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>2.047141605399588</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>-1.109530600383096</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0.7297237364532005</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0.38002618535866</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>-0.5342858823810098</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0.1097184445551093</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>-0.4205409264957652</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>-0.4414127181628802</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0.4366429732914636</v>
+        <v>-1.347530643310916</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>I7sxhAeT</t>
+          <t>UuWb8pb0</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.490019075068509</v>
+        <v>1.462522983494052</v>
       </c>
       <c r="C10" t="n">
-        <v>1.049439161371105</v>
+        <v>1.633262849589056</v>
       </c>
       <c r="D10" t="n">
-        <v>1.640946316499811</v>
+        <v>-0.3926738151284457</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2516569535949728</v>
+        <v>2.252949010740543</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2516569535947502</v>
+        <v>1.294733844586017</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9275186506963532</v>
+        <v>-0.1599887622054547</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2133967500032971</v>
+        <v>0.5406939127844487</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.803033451671221</v>
+        <v>-0.3262348909185057</v>
       </c>
       <c r="J10" t="n">
-        <v>1.139203790624439</v>
+        <v>1.162948088588168</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9270383110056515</v>
+        <v>0.5297260768144592</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4291259675631439</v>
+        <v>2.021410362998466</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04694766408297107</v>
+        <v>0.2863415062369168</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7118391858268244</v>
+        <v>0.185291481227023</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5321879751542336</v>
+        <v>-0.0628390722943693</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4779996063945601</v>
+        <v>-1.026245679464378</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.077751965687159</v>
+        <v>1.720502620765388</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.4801288031997692</v>
+        <v>-0.9018321377604931</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.504458442400608</v>
+        <v>-0.5915128176616505</v>
       </c>
       <c r="T10" t="n">
-        <v>1.581920155419731</v>
+        <v>0.7949940507316942</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1352643452547167</v>
+        <v>1.051671033674034</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.8033274238394645</v>
+        <v>-0.01064567308197746</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6787527495751372</v>
+        <v>0.5420929713267564</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1310456918139478</v>
+        <v>0.1458459403724804</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.004582398581615172</v>
+        <v>0.3951262425056489</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.03296432885695855</v>
+        <v>-0.05599840329303701</v>
       </c>
       <c r="AA10" t="n">
-        <v>-1.100533051474671</v>
+        <v>0.03729619461846728</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.7194201898017598</v>
+        <v>0.9925972902825451</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.7645892482667036</v>
+        <v>-0.7162606354206504</v>
       </c>
       <c r="AD10" t="n">
-        <v>-1.258842043285798</v>
+        <v>-0.591111455968275</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.3527178005521185</v>
+        <v>0.2656085001962197</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.6171647240046184</v>
+        <v>1.400455333478819</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.872554627994959</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-0.9938736679446682</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>-1.125085715419845</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>-0.2577579910616892</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>-1.047918650043921</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0.03204042946320033</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>-0.9091159371763048</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>2.499687521170828</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>-0.2870618567796285</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>-0.4323435736101577</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>-0.9044302570083725</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0.8378961812079954</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0.04601792547779016</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0.009880205673165195</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>-0.4214191133374336</v>
+        <v>-0.1060827493744707</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>OlK4mU3p</t>
+          <t>MFWf9Qrf</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.490019075068509</v>
+        <v>1.580643516272619</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.8323173309942289</v>
+        <v>1.683776810791356</v>
       </c>
       <c r="D11" t="n">
-        <v>1.674675000195472</v>
+        <v>-0.3926738151284457</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2516569535949728</v>
+        <v>1.471601004998859</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2516569535947502</v>
+        <v>-0.4320726842775127</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3117402208862462</v>
+        <v>-0.3364680802197836</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7920859986533954</v>
+        <v>0.2215645088513988</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.824369631888419</v>
+        <v>-1.846726115710729</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.346237160718763</v>
+        <v>0.2044337189771723</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0706374268945627</v>
+        <v>1.032922185268321</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.91160442510114</v>
+        <v>2.167781167902112</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0537982676379901</v>
+        <v>-0.3275346917081257</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4317480540653731</v>
+        <v>-1.228831957947838</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5851966051725004</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.704345853894716</v>
+        <v>-0.8344721740156805</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.580422879508985</v>
+        <v>-0.7803528224843036</v>
       </c>
       <c r="R11" t="n">
-        <v>1.030808815432247</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1363232330106567</v>
+        <v>-1.126687487653018</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3513306467105737</v>
+        <v>-0.8433475249292095</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6242105092856008</v>
+        <v>0.4524777931635737</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6282707215579836</v>
+        <v>-0.01064567308197746</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.9356372651080072</v>
+        <v>1.151169536089862</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6663248334993191</v>
+        <v>-0.1165330534091111</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.7926991191983066</v>
+        <v>-0.1397876547222189</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.513178832035002</v>
+        <v>-0.05599840329303701</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.2517752020355895</v>
+        <v>1.273816019840096</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.6495524461425821</v>
+        <v>-1.875519257375977</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.4949358069430779</v>
+        <v>-1.101967969666075</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.25361090120247</v>
+        <v>0.6237640720472275</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.6075919724537707</v>
+        <v>-0.6967281795543999</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.7625516664181186</v>
+        <v>1.869386285904428</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.5859060038580857</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>-0.2073305979989806</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0.7778581817966959</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.05115996220084684</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0.3946341266333761</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>-0.0910460757097257</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.3585227990633125</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>-0.8001690471070457</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>-2.524519342372521</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>-0.3650375958315095</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>-1.005276289060581</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0.1906270819609855</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0.03229560630209736</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0.009880205673165195</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>-0.967531360256716</v>
+        <v>-0.2927416472930742</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>6XwYhjtN</t>
+          <t>pK2NUIhs</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.509631310229416</v>
+        <v>1.462522983494052</v>
       </c>
       <c r="C12" t="n">
-        <v>1.166486215920145</v>
+        <v>1.70061479785879</v>
       </c>
       <c r="D12" t="n">
-        <v>1.640946316499811</v>
+        <v>-0.3926738151284457</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2516569535949728</v>
+        <v>-0.8046176645055608</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2516569535947502</v>
+        <v>-2.516149529457634</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.562114432562264</v>
+        <v>-2.000415935783455</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.163349240960911</v>
+        <v>-1.225020557950194</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.271145867604104</v>
+        <v>-0.9597729012485987</v>
       </c>
       <c r="J12" t="n">
-        <v>1.222051822335879</v>
+        <v>-0.2907157801988997</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.122993159888277</v>
+        <v>-0.3453975900618232</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.651617531428432</v>
+        <v>0.4858105928666476</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.239013109682579</v>
+        <v>-0.1043069833644739</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6710195202104043</v>
+        <v>-0.7072337638316932</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.314562367790741</v>
+        <v>0.8388418687743228</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2961396053062705</v>
+        <v>-0.9623211776481454</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.411998328022319</v>
+        <v>-0.06110373281547677</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1672286519834572</v>
+        <v>0.8405681559532677</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4808186709255138</v>
+        <v>0.6572280789848725</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8621541189973584</v>
+        <v>-0.05505817552887395</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7987016369933219</v>
+        <v>0.9764235104471388</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.089647052918954</v>
+        <v>-0.01064567308197746</v>
       </c>
       <c r="W12" t="n">
-        <v>-1.035754475320916</v>
+        <v>1.824601360526052</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.002358146497622</v>
+        <v>0.8919341996457163</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.04248786517039847</v>
+        <v>0.205536506779316</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.5598923894631641</v>
+        <v>0.5392361738276376</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.6497636336379178</v>
+        <v>-0.3860551944852963</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1.175744401783207</v>
+        <v>-0.114328550384975</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.3751779950017041</v>
+        <v>1.177211732693248</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0.351370276592837</v>
+        <v>1.10200078783746</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.2394403908180506</v>
+        <v>0.7030342637192287</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.8137809169765151</v>
+        <v>-0.1086467742578262</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.063577640752383</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>-0.7705640708261856</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.390238295041555</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0.001519401438498179</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>-0.08621679892572301</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0.3768990069447677</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>-0.1173884758667102</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0.1733251613963935</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>-0.795858836151772</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0.3224359020177915</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>-0.928266735996399</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>-0.8927056419989258</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>-0.3956906454490525</v>
+        <v>0.3687507562827481</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>CAvUgWQG</t>
+          <t>CWX8BehJ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.490019075068509</v>
+        <v>1.462522983494052</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.45356708206221</v>
+        <v>1.666938823723923</v>
       </c>
       <c r="D13" t="n">
-        <v>1.674675000195472</v>
+        <v>-0.3926738151284457</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2516569535949728</v>
+        <v>1.252389481165776</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2516569535947502</v>
+        <v>0.4015580537945359</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1636238892357164</v>
+        <v>-0.04653777205338628</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7572689406399091</v>
+        <v>-0.1501364538938103</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7289708186545762</v>
+        <v>-0.1995272888524871</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.973421018017283</v>
+        <v>-0.3636882466746073</v>
       </c>
       <c r="K13" t="n">
-        <v>1.35877826066797</v>
+        <v>0.114042335048225</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1937362500442377</v>
+        <v>-1.817127033275196</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3056435808293923</v>
+        <v>-0.7739901083954293</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.268138078865874</v>
+        <v>0.6865197116316738</v>
       </c>
       <c r="O13" t="n">
-        <v>1.415536663422803</v>
+        <v>1.503238351667043</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4341135593938649</v>
+        <v>-0.7705476721994482</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.171874407228749</v>
+        <v>0.9607656263245343</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.9321486887546043</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.401349785720398</v>
+        <v>0.1220534089935055</v>
       </c>
       <c r="T13" t="n">
-        <v>2.935398254980182</v>
+        <v>-0.6795133673631192</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9539719724454384</v>
+        <v>-0.03678593810594928</v>
       </c>
       <c r="V13" t="n">
-        <v>2.024078913320495</v>
+        <v>-0.01064567308197746</v>
       </c>
       <c r="W13" t="n">
-        <v>-1.498796572555616</v>
+        <v>0.03133694217530761</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.4643696503756505</v>
+        <v>-0.08269559332311306</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.096370380352168</v>
+        <v>0.4154394284763274</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.7270376836747721</v>
+        <v>-0.514360858402006</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.6497636336379178</v>
+        <v>0.7939443076838004</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.2630959778203125</v>
+        <v>0.6195500551447337</v>
       </c>
       <c r="AC13" t="n">
-        <v>-1.67792951686795</v>
+        <v>0.7038436406647731</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.8353552188290827</v>
+        <v>-0.4332704849562668</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.157030543251186</v>
+        <v>0.6155491110146269</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.4867631053318883</v>
+        <v>0.3508502568217158</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.3499125513616542</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0.203950590819667</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>-1.078455759218183</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0.5683883563241952</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0.3946341266333761</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0.05076784890259671</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>-0.3957032729903753</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>-0.2020700441066813</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>-0.3259533689496013</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>-2.961215480176765</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>-1.620023935099486</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>-2.544084862357632</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>-1.676133131071657</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>-1.343998565834971</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>-2.206439230869294</v>
+        <v>0.1012485244550169</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>llHizuVJ</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.482209738957147</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.666938823723923</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.3926738151284457</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.2173318378872081</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-1.235930895989845</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.4877360670892082</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4136263697996648</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.7063576971165615</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.777362630090626</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.01722621498321735</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3.391973354368976</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.1747276520650909</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-2.055707201089424</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.503238351667043</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-1.026245679464378</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3978209824011112</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.8138646980339039</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-1.661862157644385</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.4491600781536537</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.4161201601345351</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.01064567308197746</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.2547927049290667</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.3200256529463065</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.9638954496846475</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.5601971039129038</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0.2016950321050396</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-1.515210220511153</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.053819310523756</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.4116429481080149</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.7030342637192287</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.06294105187433861</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-0.003944336965796307</v>
       </c>
     </row>
   </sheetData>
